--- a/Data/FlightPlan/FPL_12SEP26.xlsx
+++ b/Data/FlightPlan/FPL_12SEP26.xlsx
@@ -347,10 +347,103 @@
     <t>06:10</t>
   </si>
   <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
     <t>461A *</t>
   </si>
   <si>
-    <t>VN-A524</t>
+    <t>VN-A535</t>
   </si>
   <si>
     <t>VCA</t>
@@ -383,99 +476,6 @@
     <t>20:10</t>
   </si>
   <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
     <t>VN-A536</t>
   </si>
   <si>
@@ -1208,6 +1208,9 @@
     <t>VN-A814</t>
   </si>
   <si>
+    <t>11:35</t>
+  </si>
+  <si>
     <t>SYD</t>
   </si>
   <si>
@@ -1235,10 +1238,10 @@
     <t>VN-A820</t>
   </si>
   <si>
-    <t>Total Record(s): 391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated on  Sep 12, 2026 03:19</t>
+    <t>Total Record(s): 392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated on  Sep 12, 2026 04:09</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3213,67 +3216,63 @@
       <c t="s" r="A55" s="6">
         <v>13</v>
       </c>
-      <c t="s" r="B55" s="7">
-        <v>112</v>
+      <c r="B55" s="7">
+        <v>961</v>
       </c>
       <c t="s" r="C55" s="7">
         <v>14</v>
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
+        <v>112</v>
+      </c>
+      <c r="F55" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G55" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H55" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I55" s="7">
+        <v>58</v>
+      </c>
+      <c t="s" r="J55" s="7">
         <v>113</v>
       </c>
-      <c r="F55" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G55" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H55" s="8">
-        <v>114</v>
-      </c>
-      <c t="s" r="I55" s="7">
-        <v>115</v>
-      </c>
-      <c t="s" r="J55" s="7">
-        <v>116</v>
-      </c>
-      <c t="s" r="K55" s="7">
-        <v>115</v>
-      </c>
+      <c r="K55" s="7"/>
       <c r="L55" s="7"/>
-      <c t="s" r="M55" s="7">
-        <v>116</v>
-      </c>
+      <c r="M55" s="7"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c t="s" r="A56" s="6">
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>462</v>
+        <v>946</v>
       </c>
       <c t="s" r="C56" s="7">
         <v>14</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H56" s="8">
         <v>114</v>
       </c>
-      <c t="s" r="H56" s="8">
-        <v>34</v>
-      </c>
       <c t="s" r="I56" s="7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3284,29 +3283,29 @@
         <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>525</v>
+        <v>947</v>
       </c>
       <c t="s" r="C57" s="7">
         <v>14</v>
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="H57" s="8">
         <v>34</v>
       </c>
-      <c t="s" r="H57" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I57" s="7">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3314,81 +3313,81 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c t="s" r="A58" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B58" s="7">
-        <v>528</v>
+        <v>982</v>
       </c>
       <c t="s" r="C58" s="7">
         <v>14</v>
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c t="s" r="I58" s="7">
+        <v>119</v>
+      </c>
+      <c t="s" r="J58" s="7">
         <v>120</v>
-      </c>
-      <c t="s" r="J58" s="7">
-        <v>121</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c t="s" r="A59" s="6">
-        <v>13</v>
-      </c>
-      <c r="B59" s="7">
-        <v>1157</v>
-      </c>
-      <c t="s" r="C59" s="7">
-        <v>14</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
       <c r="D59" s="7"/>
-      <c t="s" r="E59" s="7">
-        <v>113</v>
-      </c>
-      <c r="F59" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G59" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H59" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I59" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="J59" s="7">
-        <v>123</v>
-      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
+      <c t="s" r="A60" s="6">
+        <v>13</v>
+      </c>
+      <c r="B60" s="7">
+        <v>939</v>
+      </c>
+      <c t="s" r="C60" s="7">
+        <v>14</v>
+      </c>
       <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
+      <c t="s" r="E60" s="7">
+        <v>121</v>
+      </c>
+      <c r="F60" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G60" s="8">
+        <v>35</v>
+      </c>
+      <c t="s" r="H60" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I60" s="7">
+        <v>122</v>
+      </c>
+      <c t="s" r="J60" s="7">
+        <v>59</v>
+      </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
@@ -3398,26 +3397,26 @@
         <v>13</v>
       </c>
       <c r="B61" s="7">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c t="s" r="C61" s="7">
         <v>14</v>
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
+        <v>121</v>
+      </c>
+      <c r="F61" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G61" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H61" s="8">
+        <v>123</v>
+      </c>
+      <c t="s" r="I61" s="7">
         <v>124</v>
-      </c>
-      <c r="F61" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G61" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H61" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="I61" s="7">
-        <v>58</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>125</v>
@@ -3431,29 +3430,29 @@
         <v>13</v>
       </c>
       <c r="B62" s="7">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c t="s" r="C62" s="7">
         <v>14</v>
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
+        <v>123</v>
+      </c>
+      <c t="s" r="H62" s="8">
         <v>34</v>
       </c>
-      <c t="s" r="H62" s="8">
+      <c t="s" r="I62" s="7">
+        <v>71</v>
+      </c>
+      <c t="s" r="J62" s="7">
         <v>126</v>
-      </c>
-      <c t="s" r="I62" s="7">
-        <v>127</v>
-      </c>
-      <c t="s" r="J62" s="7">
-        <v>128</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3461,81 +3460,81 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c t="s" r="A63" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B63" s="7">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c t="s" r="C63" s="7">
         <v>14</v>
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c t="s" r="A64" s="6">
-        <v>43</v>
-      </c>
-      <c r="B64" s="7">
-        <v>982</v>
-      </c>
-      <c t="s" r="C64" s="7">
-        <v>14</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="7"/>
-      <c t="s" r="E64" s="7">
-        <v>124</v>
-      </c>
-      <c r="F64" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G64" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H64" s="8">
-        <v>56</v>
-      </c>
-      <c t="s" r="I64" s="7">
-        <v>131</v>
-      </c>
-      <c t="s" r="J64" s="7">
-        <v>132</v>
-      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
+      <c t="s" r="A65" s="6">
+        <v>13</v>
+      </c>
+      <c r="B65" s="7">
+        <v>501</v>
+      </c>
+      <c t="s" r="C65" s="7">
+        <v>14</v>
+      </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
+      <c t="s" r="E65" s="7">
+        <v>129</v>
+      </c>
+      <c r="F65" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G65" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H65" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I65" s="7">
+        <v>32</v>
+      </c>
+      <c t="s" r="J65" s="7">
+        <v>130</v>
+      </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
@@ -3545,29 +3544,29 @@
         <v>13</v>
       </c>
       <c r="B66" s="7">
-        <v>939</v>
+        <v>514</v>
       </c>
       <c t="s" r="C66" s="7">
         <v>14</v>
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3578,14 +3577,14 @@
         <v>13</v>
       </c>
       <c r="B67" s="7">
-        <v>948</v>
+        <v>563</v>
       </c>
       <c t="s" r="C67" s="7">
         <v>14</v>
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3594,13 +3593,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3611,29 +3610,29 @@
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>949</v>
+        <v>564</v>
       </c>
       <c t="s" r="C68" s="7">
         <v>14</v>
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3641,17 +3640,17 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c t="s" r="A69" s="6">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>938</v>
+        <v>567</v>
       </c>
       <c t="s" r="C69" s="7">
         <v>14</v>
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3660,29 +3659,47 @@
         <v>34</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c r="M69" s="7"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
+      <c t="s" r="A70" s="6">
+        <v>13</v>
+      </c>
+      <c r="B70" s="7">
+        <v>568</v>
+      </c>
+      <c t="s" r="C70" s="7">
+        <v>14</v>
+      </c>
       <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
+      <c t="s" r="E70" s="7">
+        <v>129</v>
+      </c>
+      <c r="F70" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G70" s="8">
+        <v>132</v>
+      </c>
+      <c t="s" r="H70" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I70" s="7">
+        <v>138</v>
+      </c>
+      <c t="s" r="J70" s="7">
+        <v>139</v>
+      </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c r="M70" s="7"/>
@@ -3692,14 +3709,14 @@
         <v>13</v>
       </c>
       <c r="B71" s="7">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c t="s" r="C71" s="7">
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3711,10 +3728,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3725,14 +3742,14 @@
         <v>13</v>
       </c>
       <c r="B72" s="7">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c t="s" r="C72" s="7">
         <v>14</v>
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3744,44 +3761,26 @@
         <v>34</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c t="s" r="A73" s="6">
-        <v>13</v>
-      </c>
-      <c r="B73" s="7">
-        <v>563</v>
-      </c>
-      <c t="s" r="C73" s="7">
-        <v>14</v>
-      </c>
+      <c r="A73" s="6"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
       <c r="D73" s="7"/>
-      <c t="s" r="E73" s="7">
-        <v>141</v>
-      </c>
-      <c r="F73" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G73" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H73" s="8">
-        <v>144</v>
-      </c>
-      <c t="s" r="I73" s="7">
-        <v>64</v>
-      </c>
-      <c t="s" r="J73" s="7">
-        <v>145</v>
-      </c>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
@@ -3790,24 +3789,24 @@
       <c t="s" r="A74" s="6">
         <v>13</v>
       </c>
-      <c r="B74" s="7">
-        <v>564</v>
+      <c t="s" r="B74" s="7">
+        <v>143</v>
       </c>
       <c t="s" r="C74" s="7">
         <v>14</v>
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c t="s" r="I74" s="7">
         <v>146</v>
@@ -3815,32 +3814,36 @@
       <c t="s" r="J74" s="7">
         <v>147</v>
       </c>
-      <c r="K74" s="7"/>
+      <c t="s" r="K74" s="7">
+        <v>146</v>
+      </c>
       <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
+      <c t="s" r="M74" s="7">
+        <v>147</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c t="s" r="A75" s="6">
         <v>13</v>
       </c>
       <c r="B75" s="7">
-        <v>567</v>
+        <v>462</v>
       </c>
       <c t="s" r="C75" s="7">
         <v>14</v>
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
+        <v>145</v>
+      </c>
+      <c t="s" r="H75" s="8">
         <v>34</v>
-      </c>
-      <c t="s" r="H75" s="8">
-        <v>144</v>
       </c>
       <c t="s" r="I75" s="7">
         <v>148</v>
@@ -3857,29 +3860,29 @@
         <v>13</v>
       </c>
       <c r="B76" s="7">
-        <v>568</v>
+        <v>525</v>
       </c>
       <c t="s" r="C76" s="7">
         <v>14</v>
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>150</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3890,29 +3893,29 @@
         <v>13</v>
       </c>
       <c r="B77" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c t="s" r="C77" s="7">
         <v>14</v>
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H77" s="8">
         <v>34</v>
       </c>
-      <c t="s" r="H77" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I77" s="7">
+        <v>151</v>
+      </c>
+      <c t="s" r="J77" s="7">
         <v>152</v>
-      </c>
-      <c t="s" r="J77" s="7">
-        <v>61</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3923,23 +3926,23 @@
         <v>13</v>
       </c>
       <c r="B78" s="7">
-        <v>526</v>
+        <v>1157</v>
       </c>
       <c t="s" r="C78" s="7">
         <v>14</v>
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>153</v>
@@ -4023,7 +4026,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>71</v>
@@ -4137,13 +4140,13 @@
         <v>97</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>160</v>
       </c>
       <c t="s" r="K85" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
@@ -4354,7 +4357,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>78</v>
@@ -4471,7 +4474,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4501,10 +4504,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4612,7 +4615,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="I101" s="7">
         <v>177</v>
@@ -4642,7 +4645,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>25</v>
@@ -4678,7 +4681,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c t="s" r="I103" s="7">
         <v>96</v>
@@ -4708,7 +4711,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>25</v>
@@ -5122,10 +5125,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5158,7 +5161,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5221,7 +5224,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>203</v>
@@ -5269,13 +5272,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>106</v>
       </c>
       <c t="s" r="K123" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
@@ -5453,7 +5456,7 @@
         <v>212</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>213</v>
@@ -5567,7 +5570,7 @@
         <v>217</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>172</v>
@@ -5600,7 +5603,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>218</v>
@@ -5636,7 +5639,7 @@
         <v>219</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5666,7 +5669,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>220</v>
@@ -5702,7 +5705,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5962,7 +5965,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>64</v>
@@ -6160,7 +6163,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6454,7 +6457,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6517,7 +6520,7 @@
         <v>246</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>90</v>
@@ -6550,7 +6553,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>247</v>
@@ -6664,7 +6667,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>250</v>
@@ -6733,7 +6736,7 @@
         <v>252</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6760,10 +6763,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>51</v>
@@ -6790,7 +6793,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>34</v>
@@ -6907,7 +6910,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>256</v>
@@ -6937,7 +6940,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>16</v>
@@ -7237,7 +7240,7 @@
         <v>260</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>255</v>
@@ -7300,13 +7303,13 @@
         <v>246</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>258</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7330,7 +7333,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>246</v>
@@ -7450,7 +7453,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>84</v>
@@ -7519,7 +7522,7 @@
         <v>230</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7630,13 +7633,13 @@
         <v>217</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>57</v>
       </c>
       <c t="s" r="K202" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
@@ -7697,13 +7700,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>264</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7727,7 +7730,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>25</v>
@@ -7766,7 +7769,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>284</v>
@@ -7799,10 +7802,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7865,7 +7868,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>156</v>
@@ -7949,7 +7952,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8195,7 +8198,7 @@
         <v>287</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8273,7 +8276,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>211</v>
@@ -8441,7 +8444,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8654,7 +8657,7 @@
         <v>296</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8897,7 +8900,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>307</v>
@@ -8975,7 +8978,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>95</v>
@@ -9005,13 +9008,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>257</v>
@@ -9293,7 +9296,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9323,7 +9326,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>297</v>
@@ -9440,7 +9443,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9503,10 +9506,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9554,7 +9557,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9716,7 +9719,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>222</v>
@@ -9797,7 +9800,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>237</v>
@@ -9827,10 +9830,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>84</v>
@@ -9857,7 +9860,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>25</v>
@@ -9962,7 +9965,7 @@
         <v>323</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>92</v>
@@ -9995,7 +9998,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>324</v>
@@ -10142,7 +10145,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>49</v>
@@ -10175,10 +10178,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10259,7 +10262,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10289,7 +10292,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>283</v>
@@ -10355,7 +10358,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>156</v>
@@ -10613,7 +10616,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>293</v>
@@ -10643,7 +10646,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>34</v>
@@ -10718,7 +10721,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10796,7 +10799,7 @@
         <v>260</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>172</v>
@@ -10829,7 +10832,7 @@
         <v>168</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>84</v>
@@ -11108,7 +11111,7 @@
         <v>320</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>84</v>
@@ -11171,7 +11174,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>252</v>
@@ -11201,7 +11204,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>25</v>
@@ -11354,10 +11357,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11423,7 +11426,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11687,7 +11690,7 @@
         <v>106</v>
       </c>
       <c t="s" r="K335" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
@@ -11718,7 +11721,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>347</v>
@@ -11754,7 +11757,7 @@
         <v>348</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11898,10 +11901,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11997,7 +12000,7 @@
         <v>323</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>198</v>
@@ -12030,7 +12033,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>351</v>
@@ -12327,7 +12330,7 @@
         <v>310</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12408,7 +12411,7 @@
         <v>324</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12621,7 +12624,7 @@
         <v>273</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12684,7 +12687,7 @@
         <v>246</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>275</v>
@@ -12933,7 +12936,7 @@
         <v>219</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13077,7 +13080,7 @@
         <v>305</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>179</v>
@@ -13110,7 +13113,7 @@
         <v>168</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>369</v>
@@ -13176,7 +13179,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>220</v>
@@ -13212,7 +13215,7 @@
         <v>348</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13356,7 +13359,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>348</v>
@@ -13605,7 +13608,7 @@
         <v>257</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13635,7 +13638,7 @@
         <v>276</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>374</v>
@@ -13851,7 +13854,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14094,7 +14097,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>294</v>
@@ -14127,10 +14130,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14274,7 +14277,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>245</v>
@@ -14406,7 +14409,7 @@
         <v>301</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>371</v>
@@ -14682,7 +14685,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="I433" s="7">
         <v>28</v>
@@ -14712,7 +14715,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>25</v>
@@ -14883,7 +14886,7 @@
         <v>308</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15015,7 +15018,7 @@
         <v>238</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15093,7 +15096,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>365</v>
@@ -15240,7 +15243,7 @@
         <v>305</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>38</v>
@@ -15324,7 +15327,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15435,7 +15438,7 @@
         <v>397</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>108</v>
@@ -15497,7 +15500,7 @@
         <v>13</v>
       </c>
       <c r="B462" s="7">
-        <v>609</v>
+        <v>5061</v>
       </c>
       <c t="s" r="C462" s="7">
         <v>14</v>
@@ -15510,27 +15513,29 @@
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
+        <v>397</v>
+      </c>
+      <c t="s" r="H462" s="8">
         <v>76</v>
       </c>
-      <c t="s" r="H462" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I462" s="7">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>252</v>
+        <v>399</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
-      <c r="M462" s="7"/>
+      <c t="s" r="M462" s="7">
+        <v>134</v>
+      </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
       <c t="s" r="A463" s="6">
         <v>13</v>
       </c>
       <c r="B463" s="7">
-        <v>85</v>
+        <v>609</v>
       </c>
       <c t="s" r="C463" s="7">
         <v>14</v>
@@ -15543,65 +15548,65 @@
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>399</v>
+        <v>25</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>142</v>
+        <v>252</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c r="M463" s="7"/>
     </row>
     <row r="464" ht="14.25" customHeight="1">
-      <c r="A464" s="6"/>
-      <c r="B464" s="7"/>
-      <c r="C464" s="7"/>
+      <c t="s" r="A464" s="6">
+        <v>13</v>
+      </c>
+      <c r="B464" s="7">
+        <v>85</v>
+      </c>
+      <c t="s" r="C464" s="7">
+        <v>14</v>
+      </c>
       <c r="D464" s="7"/>
-      <c r="E464" s="7"/>
-      <c r="F464" s="7"/>
-      <c r="G464" s="8"/>
-      <c r="H464" s="8"/>
-      <c r="I464" s="7"/>
-      <c r="J464" s="7"/>
+      <c t="s" r="E464" s="7">
+        <v>398</v>
+      </c>
+      <c r="F464" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G464" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H464" s="8">
+        <v>400</v>
+      </c>
+      <c t="s" r="I464" s="7">
+        <v>140</v>
+      </c>
+      <c t="s" r="J464" s="7">
+        <v>130</v>
+      </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c r="M464" s="7"/>
     </row>
     <row r="465" ht="15" customHeight="1">
-      <c t="s" r="A465" s="6">
-        <v>13</v>
-      </c>
-      <c r="B465" s="7">
-        <v>1624</v>
-      </c>
-      <c t="s" r="C465" s="7">
-        <v>14</v>
-      </c>
+      <c r="A465" s="6"/>
+      <c r="B465" s="7"/>
+      <c r="C465" s="7"/>
       <c r="D465" s="7"/>
-      <c t="s" r="E465" s="7">
-        <v>400</v>
-      </c>
-      <c r="F465" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G465" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H465" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I465" s="7">
-        <v>290</v>
-      </c>
-      <c t="s" r="J465" s="7">
-        <v>256</v>
-      </c>
+      <c r="E465" s="7"/>
+      <c r="F465" s="7"/>
+      <c r="G465" s="8"/>
+      <c r="H465" s="8"/>
+      <c r="I465" s="7"/>
+      <c r="J465" s="7"/>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c r="M465" s="7"/>
@@ -15611,29 +15616,29 @@
         <v>13</v>
       </c>
       <c r="B466" s="7">
-        <v>55</v>
+        <v>1624</v>
       </c>
       <c t="s" r="C466" s="7">
         <v>14</v>
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H466" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H466" s="8">
-        <v>401</v>
-      </c>
       <c t="s" r="I466" s="7">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>380</v>
+        <v>256</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -15644,78 +15649,78 @@
         <v>13</v>
       </c>
       <c r="B467" s="7">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c t="s" r="C467" s="7">
         <v>14</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>401</v>
+        <v>16</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>16</v>
+        <v>402</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>390</v>
+        <v>258</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c r="M467" s="7"/>
     </row>
     <row r="468" ht="14.25" customHeight="1">
-      <c r="A468" s="6"/>
-      <c r="B468" s="7"/>
-      <c r="C468" s="7"/>
+      <c t="s" r="A468" s="6">
+        <v>13</v>
+      </c>
+      <c r="B468" s="7">
+        <v>56</v>
+      </c>
+      <c t="s" r="C468" s="7">
+        <v>14</v>
+      </c>
       <c r="D468" s="7"/>
-      <c r="E468" s="7"/>
-      <c r="F468" s="7"/>
-      <c r="G468" s="8"/>
-      <c r="H468" s="8"/>
-      <c r="I468" s="7"/>
-      <c r="J468" s="7"/>
+      <c t="s" r="E468" s="7">
+        <v>401</v>
+      </c>
+      <c r="F468" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G468" s="8">
+        <v>402</v>
+      </c>
+      <c t="s" r="H468" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I468" s="7">
+        <v>390</v>
+      </c>
+      <c t="s" r="J468" s="7">
+        <v>194</v>
+      </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c r="M468" s="7"/>
     </row>
     <row r="469" ht="14.25" customHeight="1">
-      <c t="s" r="A469" s="6">
-        <v>13</v>
-      </c>
-      <c r="B469" s="7">
-        <v>8931</v>
-      </c>
-      <c t="s" r="C469" s="7">
-        <v>14</v>
-      </c>
+      <c r="A469" s="6"/>
+      <c r="B469" s="7"/>
+      <c r="C469" s="7"/>
       <c r="D469" s="7"/>
-      <c t="s" r="E469" s="7">
-        <v>402</v>
-      </c>
-      <c r="F469" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G469" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H469" s="8">
-        <v>403</v>
-      </c>
-      <c t="s" r="I469" s="7">
-        <v>132</v>
-      </c>
-      <c t="s" r="J469" s="7">
-        <v>283</v>
-      </c>
+      <c r="E469" s="7"/>
+      <c r="F469" s="7"/>
+      <c r="G469" s="8"/>
+      <c r="H469" s="8"/>
+      <c r="I469" s="7"/>
+      <c r="J469" s="7"/>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c r="M469" s="7"/>
@@ -15725,78 +15730,78 @@
         <v>13</v>
       </c>
       <c r="B470" s="7">
-        <v>8932</v>
+        <v>8931</v>
       </c>
       <c t="s" r="C470" s="7">
         <v>14</v>
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>403</v>
+        <v>16</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>258</v>
+        <v>120</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c r="M470" s="7"/>
     </row>
     <row r="471" ht="14.25" customHeight="1">
-      <c r="A471" s="6"/>
-      <c r="B471" s="7"/>
-      <c r="C471" s="7"/>
+      <c t="s" r="A471" s="6">
+        <v>13</v>
+      </c>
+      <c r="B471" s="7">
+        <v>8932</v>
+      </c>
+      <c t="s" r="C471" s="7">
+        <v>14</v>
+      </c>
       <c r="D471" s="7"/>
-      <c r="E471" s="7"/>
-      <c r="F471" s="7"/>
-      <c r="G471" s="8"/>
-      <c r="H471" s="8"/>
-      <c r="I471" s="7"/>
-      <c r="J471" s="7"/>
+      <c t="s" r="E471" s="7">
+        <v>403</v>
+      </c>
+      <c r="F471" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G471" s="8">
+        <v>404</v>
+      </c>
+      <c t="s" r="H471" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I471" s="7">
+        <v>258</v>
+      </c>
+      <c t="s" r="J471" s="7">
+        <v>177</v>
+      </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
       <c r="M471" s="7"/>
     </row>
     <row r="472" ht="14.25" customHeight="1">
-      <c t="s" r="A472" s="6">
-        <v>13</v>
-      </c>
-      <c r="B472" s="7">
-        <v>83</v>
-      </c>
-      <c t="s" r="C472" s="7">
-        <v>14</v>
-      </c>
+      <c r="A472" s="6"/>
+      <c r="B472" s="7"/>
+      <c r="C472" s="7"/>
       <c r="D472" s="7"/>
-      <c t="s" r="E472" s="7">
-        <v>404</v>
-      </c>
-      <c r="F472" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G472" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H472" s="8">
-        <v>405</v>
-      </c>
-      <c t="s" r="I472" s="7">
-        <v>245</v>
-      </c>
-      <c t="s" r="J472" s="7">
-        <v>203</v>
-      </c>
+      <c r="E472" s="7"/>
+      <c r="F472" s="7"/>
+      <c r="G472" s="8"/>
+      <c r="H472" s="8"/>
+      <c r="I472" s="7"/>
+      <c r="J472" s="7"/>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c r="M472" s="7"/>
@@ -15806,124 +15811,157 @@
         <v>13</v>
       </c>
       <c r="B473" s="7">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c t="s" r="C473" s="7">
         <v>14</v>
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>405</v>
+        <v>25</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>25</v>
+        <v>406</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>406</v>
+        <v>245</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>324</v>
+        <v>203</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
       <c r="M473" s="7"/>
     </row>
     <row r="474" ht="14.25" customHeight="1">
-      <c r="A474" s="6"/>
-      <c r="B474" s="7"/>
-      <c r="C474" s="7"/>
+      <c t="s" r="A474" s="6">
+        <v>13</v>
+      </c>
+      <c r="B474" s="7">
+        <v>84</v>
+      </c>
+      <c t="s" r="C474" s="7">
+        <v>14</v>
+      </c>
       <c r="D474" s="7"/>
-      <c r="E474" s="7"/>
-      <c r="F474" s="7"/>
-      <c r="G474" s="8"/>
-      <c r="H474" s="8"/>
-      <c r="I474" s="7"/>
-      <c r="J474" s="7"/>
+      <c t="s" r="E474" s="7">
+        <v>405</v>
+      </c>
+      <c r="F474" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G474" s="8">
+        <v>406</v>
+      </c>
+      <c t="s" r="H474" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I474" s="7">
+        <v>407</v>
+      </c>
+      <c t="s" r="J474" s="7">
+        <v>324</v>
+      </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
       <c r="M474" s="7"/>
     </row>
     <row r="475" ht="15" customHeight="1">
-      <c t="s" r="A475" s="6">
-        <v>13</v>
-      </c>
-      <c r="B475" s="7">
-        <v>1626</v>
-      </c>
-      <c t="s" r="C475" s="7">
-        <v>14</v>
-      </c>
+      <c r="A475" s="6"/>
+      <c r="B475" s="7"/>
+      <c r="C475" s="7"/>
       <c r="D475" s="7"/>
-      <c t="s" r="E475" s="7">
-        <v>407</v>
-      </c>
-      <c r="F475" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G475" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H475" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I475" s="7">
-        <v>85</v>
-      </c>
-      <c t="s" r="J475" s="7">
-        <v>294</v>
-      </c>
+      <c r="E475" s="7"/>
+      <c r="F475" s="7"/>
+      <c r="G475" s="8"/>
+      <c r="H475" s="8"/>
+      <c r="I475" s="7"/>
+      <c r="J475" s="7"/>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
       <c r="M475" s="7"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
-      <c t="s" r="A476" s="9">
+    <row r="476" ht="14.25" customHeight="1">
+      <c t="s" r="A476" s="6">
+        <v>13</v>
+      </c>
+      <c r="B476" s="7">
+        <v>1626</v>
+      </c>
+      <c t="s" r="C476" s="7">
+        <v>14</v>
+      </c>
+      <c r="D476" s="7"/>
+      <c t="s" r="E476" s="7">
         <v>408</v>
       </c>
-      <c r="B476" s="9"/>
-      <c r="C476" s="9"/>
-      <c r="D476" s="9"/>
-      <c r="E476" s="9"/>
-      <c r="F476" s="9"/>
-      <c r="G476" s="9"/>
-      <c r="H476" s="9"/>
-      <c r="I476" s="9"/>
-      <c r="J476" s="9"/>
-      <c r="K476" s="9"/>
-      <c r="L476" s="9"/>
-      <c r="M476" s="9"/>
-      <c r="N476" s="9"/>
-      <c r="O476" s="9"/>
-    </row>
-    <row r="477" ht="65.25" customHeight="1"/>
-    <row r="478" ht="16.5" customHeight="1">
-      <c t="s" r="A478" s="10">
+      <c r="F476" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G476" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H476" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I476" s="7">
+        <v>85</v>
+      </c>
+      <c t="s" r="J476" s="7">
+        <v>294</v>
+      </c>
+      <c r="K476" s="7"/>
+      <c r="L476" s="7"/>
+      <c r="M476" s="7"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c t="s" r="A477" s="9">
         <v>409</v>
       </c>
-      <c r="B478" s="10"/>
-      <c r="C478" s="10"/>
-      <c r="D478" s="10"/>
-      <c r="E478" s="10"/>
-      <c r="F478" s="10"/>
-      <c r="G478" s="10"/>
-      <c r="H478" s="10"/>
-      <c r="I478" s="10"/>
-      <c r="J478" s="10"/>
-      <c r="K478" s="10"/>
-      <c t="s" r="L478" s="11">
+      <c r="B477" s="9"/>
+      <c r="C477" s="9"/>
+      <c r="D477" s="9"/>
+      <c r="E477" s="9"/>
+      <c r="F477" s="9"/>
+      <c r="G477" s="9"/>
+      <c r="H477" s="9"/>
+      <c r="I477" s="9"/>
+      <c r="J477" s="9"/>
+      <c r="K477" s="9"/>
+      <c r="L477" s="9"/>
+      <c r="M477" s="9"/>
+      <c r="N477" s="9"/>
+      <c r="O477" s="9"/>
+    </row>
+    <row r="478" ht="65.25" customHeight="1"/>
+    <row r="479" ht="16.5" customHeight="1">
+      <c t="s" r="A479" s="10">
         <v>410</v>
       </c>
-      <c r="M478" s="11"/>
-      <c r="N478" s="11"/>
+      <c r="B479" s="10"/>
+      <c r="C479" s="10"/>
+      <c r="D479" s="10"/>
+      <c r="E479" s="10"/>
+      <c r="F479" s="10"/>
+      <c r="G479" s="10"/>
+      <c r="H479" s="10"/>
+      <c r="I479" s="10"/>
+      <c r="J479" s="10"/>
+      <c r="K479" s="10"/>
+      <c t="s" r="L479" s="11">
+        <v>411</v>
+      </c>
+      <c r="M479" s="11"/>
+      <c r="N479" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="946">
+  <mergeCells count="948">
     <mergeCell ref="D1:O1"/>
     <mergeCell ref="D2:O2"/>
     <mergeCell ref="D3:O4"/>
@@ -16867,9 +16905,11 @@
     <mergeCell ref="K474:L474"/>
     <mergeCell ref="C475:D475"/>
     <mergeCell ref="K475:L475"/>
-    <mergeCell ref="A476:O476"/>
-    <mergeCell ref="A478:K478"/>
-    <mergeCell ref="L478:N478"/>
+    <mergeCell ref="C476:D476"/>
+    <mergeCell ref="K476:L476"/>
+    <mergeCell ref="A477:O477"/>
+    <mergeCell ref="A479:K479"/>
+    <mergeCell ref="L479:N479"/>
   </mergeCells>
   <pageMargins left="0.196666672825813" right="0.219999998807907" top="0.280000001192093" bottom="0.230000004172325" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/Data/FlightPlan/FPL_12SEP26.xlsx
+++ b/Data/FlightPlan/FPL_12SEP26.xlsx
@@ -404,21 +404,36 @@
     <t>07:20</t>
   </si>
   <si>
+    <t>06:45</t>
+  </si>
+  <si>
     <t>09:10</t>
   </si>
   <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
     <t>HUI</t>
   </si>
   <si>
     <t>10:55</t>
   </si>
   <si>
+    <t>11:55</t>
+  </si>
+  <si>
     <t>11:25</t>
   </si>
   <si>
     <t>12:40</t>
   </si>
   <si>
+    <t>12:25</t>
+  </si>
+  <si>
     <t>15:55</t>
   </si>
   <si>
@@ -458,9 +473,6 @@
     <t>09:45</t>
   </si>
   <si>
-    <t>11:55</t>
-  </si>
-  <si>
     <t>14:05</t>
   </si>
   <si>
@@ -533,9 +545,6 @@
     <t>VN-A543</t>
   </si>
   <si>
-    <t>08:45</t>
-  </si>
-  <si>
     <t>BOM</t>
   </si>
   <si>
@@ -656,9 +665,6 @@
     <t>VN-A553</t>
   </si>
   <si>
-    <t>06:45</t>
-  </si>
-  <si>
     <t>08:30</t>
   </si>
   <si>
@@ -752,159 +758,156 @@
     <t>VN-A629</t>
   </si>
   <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
     <t>08:40</t>
   </si>
   <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>392A *</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
     <t>14:10</t>
   </si>
   <si>
     <t>16:20</t>
   </si>
   <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>392A *</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
     <t>VN-A642</t>
   </si>
   <si>
@@ -1064,7 +1067,7 @@
     <t>06:25</t>
   </si>
   <si>
-    <t>10:07</t>
+    <t>09:21</t>
   </si>
   <si>
     <t>16:45</t>
@@ -1103,9 +1106,6 @@
     <t>08:25</t>
   </si>
   <si>
-    <t>10:05</t>
-  </si>
-  <si>
     <t>17:35</t>
   </si>
   <si>
@@ -1205,6 +1205,9 @@
     <t>VN-A697</t>
   </si>
   <si>
+    <t>06:43</t>
+  </si>
+  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1229,7 +1232,7 @@
     <t>11:35</t>
   </si>
   <si>
-    <t>11:43</t>
+    <t>11:29</t>
   </si>
   <si>
     <t>SYD</t>
@@ -1262,7 +1265,7 @@
     <t>Total Record(s): 392</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 12, 2026 05:15</t>
+    <t xml:space="preserve">Generated on  Sep 12, 2026 05:32</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3556,9 +3559,13 @@
       <c t="s" r="J65" s="7">
         <v>130</v>
       </c>
-      <c r="K65" s="7"/>
+      <c t="s" r="K65" s="7">
+        <v>131</v>
+      </c>
       <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
+      <c t="s" r="M65" s="7">
+        <v>57</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c t="s" r="A66" s="6">
@@ -3587,11 +3594,15 @@
         <v>128</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>131</v>
-      </c>
-      <c r="K66" s="7"/>
+        <v>132</v>
+      </c>
+      <c t="s" r="K66" s="7">
+        <v>133</v>
+      </c>
       <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
+      <c t="s" r="M66" s="7">
+        <v>134</v>
+      </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c t="s" r="A67" s="6">
@@ -3614,17 +3625,21 @@
         <v>34</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I67" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>133</v>
-      </c>
-      <c r="K67" s="7"/>
+        <v>136</v>
+      </c>
+      <c t="s" r="K67" s="7">
+        <v>84</v>
+      </c>
       <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
+      <c t="s" r="M67" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c t="s" r="A68" s="6">
@@ -3644,20 +3659,24 @@
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>135</v>
-      </c>
-      <c r="K68" s="7"/>
+        <v>139</v>
+      </c>
+      <c t="s" r="K68" s="7">
+        <v>140</v>
+      </c>
       <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
+      <c t="s" r="M68" s="7">
+        <v>98</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c t="s" r="A69" s="6">
@@ -3680,13 +3699,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3710,16 +3729,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3749,7 +3768,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>61</v>
@@ -3782,10 +3801,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3811,14 +3830,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B74" s="7">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c t="s" r="C74" s="7">
         <v>14</v>
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3827,20 +3846,20 @@
         <v>34</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c t="s" r="K74" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -3855,22 +3874,22 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3888,7 +3907,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3900,7 +3919,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>38</v>
@@ -3921,7 +3940,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3933,10 +3952,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3954,7 +3973,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3966,10 +3985,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4002,7 +4021,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4035,7 +4054,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4068,7 +4087,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4083,7 +4102,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4101,7 +4120,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4116,7 +4135,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4142,14 +4161,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B85" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4161,13 +4180,13 @@
         <v>97</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="K85" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
@@ -4186,7 +4205,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4201,7 +4220,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4219,7 +4238,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4228,13 +4247,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4252,22 +4271,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4285,7 +4304,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4297,7 +4316,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>91</v>
@@ -4333,7 +4352,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4342,13 +4361,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4366,13 +4385,13 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>25</v>
@@ -4399,7 +4418,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4408,10 +4427,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>101</v>
@@ -4432,19 +4451,19 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>52</v>
@@ -4480,7 +4499,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4492,7 +4511,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>113</v>
@@ -4513,7 +4532,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4528,7 +4547,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4546,7 +4565,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4555,13 +4574,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4579,19 +4598,19 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>18</v>
@@ -4627,7 +4646,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4636,20 +4655,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="K101" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -4664,29 +4683,29 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="K102" s="7">
         <v>106</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -4701,7 +4720,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4719,7 +4738,7 @@
         <v>37</v>
       </c>
       <c t="s" r="K103" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
@@ -4738,7 +4757,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4756,11 +4775,11 @@
         <v>71</v>
       </c>
       <c t="s" r="K104" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -4775,7 +4794,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4784,7 +4803,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="I105" s="7">
         <v>28</v>
@@ -4808,22 +4827,22 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4856,22 +4875,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4889,7 +4908,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4904,7 +4923,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4922,7 +4941,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4937,7 +4956,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4955,7 +4974,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4967,10 +4986,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4988,7 +5007,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5000,10 +5019,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5021,7 +5040,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5030,13 +5049,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5069,7 +5088,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5081,7 +5100,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>31</v>
@@ -5102,7 +5121,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5111,13 +5130,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5150,7 +5169,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5162,7 +5181,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>113</v>
@@ -5183,7 +5202,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5195,10 +5214,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5216,7 +5235,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5228,10 +5247,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5249,7 +5268,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5261,10 +5280,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5290,14 +5309,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B123" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="C123" s="7">
         <v>14</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5309,13 +5328,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>106</v>
       </c>
       <c t="s" r="K123" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
@@ -5334,7 +5353,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5346,10 +5365,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5367,7 +5386,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5379,10 +5398,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5400,7 +5419,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5415,7 +5434,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5448,7 +5467,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5460,10 +5479,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>215</v>
+        <v>131</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5481,7 +5500,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5490,13 +5509,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5514,19 +5533,19 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>44</v>
@@ -5547,7 +5566,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5559,10 +5578,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5595,7 +5614,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5604,13 +5623,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I133" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5628,22 +5647,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5661,7 +5680,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5676,7 +5695,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5694,7 +5713,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5706,7 +5725,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>71</v>
@@ -5727,7 +5746,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5742,7 +5761,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5760,7 +5779,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5775,7 +5794,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5808,7 +5827,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5817,13 +5836,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5841,22 +5860,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5874,7 +5893,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5886,7 +5905,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>124</v>
@@ -5907,7 +5926,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5919,10 +5938,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5940,7 +5959,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5952,7 +5971,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>116</v>
@@ -5973,7 +5992,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5985,7 +6004,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>44</v>
@@ -6006,7 +6025,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6015,13 +6034,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6054,7 +6073,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6066,15 +6085,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6089,7 +6108,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6101,10 +6120,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6122,7 +6141,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6137,7 +6156,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6155,7 +6174,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6203,7 +6222,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6215,7 +6234,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>64</v>
@@ -6223,7 +6242,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6253,19 +6272,19 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>99</v>
@@ -6286,7 +6305,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6298,7 +6317,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>36</v>
@@ -6334,7 +6353,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6346,28 +6365,32 @@
         <v>25</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>204</v>
-      </c>
-      <c r="K158" s="7"/>
+        <v>207</v>
+      </c>
+      <c t="s" r="K158" s="7">
+        <v>32</v>
+      </c>
       <c r="L158" s="7"/>
-      <c r="M158" s="7"/>
+      <c t="s" r="M158" s="7">
+        <v>57</v>
+      </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c t="s" r="A159" s="6">
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>130</v>
+        <v>825</v>
       </c>
       <c t="s" r="C159" s="7">
         <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6376,13 +6399,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>34</v>
+        <v>249</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>247</v>
+        <v>67</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6393,29 +6416,29 @@
         <v>13</v>
       </c>
       <c r="B160" s="7">
-        <v>133</v>
+        <v>826</v>
       </c>
       <c t="s" r="C160" s="7">
         <v>14</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>34</v>
+        <v>249</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>124</v>
+        <v>251</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6426,14 +6449,14 @@
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>140</v>
+        <v>805</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6442,13 +6465,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6459,29 +6482,29 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>151</v>
+        <v>806</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6514,7 +6537,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6523,10 +6546,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>85</v>
@@ -6547,13 +6570,13 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>34</v>
@@ -6562,7 +6585,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6580,7 +6603,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6592,10 +6615,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6628,7 +6651,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6637,10 +6660,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>57</v>
@@ -6661,22 +6684,22 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6694,7 +6717,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6727,7 +6750,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6760,7 +6783,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6769,10 +6792,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>90</v>
@@ -6793,22 +6816,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6826,7 +6849,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6841,7 +6864,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6874,7 +6897,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6889,7 +6912,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6907,7 +6930,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6919,10 +6942,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6940,7 +6963,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6952,7 +6975,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>98</v>
@@ -6973,7 +6996,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6985,10 +7008,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7006,7 +7029,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7015,7 +7038,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>125</v>
@@ -7039,13 +7062,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>34</v>
@@ -7054,7 +7077,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7087,7 +7110,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7096,13 +7119,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7120,13 +7143,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>16</v>
@@ -7135,7 +7158,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7153,7 +7176,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7162,13 +7185,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7186,19 +7209,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>50</v>
@@ -7234,7 +7257,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7243,13 +7266,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="I188" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7267,22 +7290,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7300,7 +7323,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7309,13 +7332,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7333,19 +7356,19 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>37</v>
@@ -7366,7 +7389,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7375,10 +7398,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>88</v>
@@ -7399,19 +7422,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>80</v>
@@ -7447,7 +7470,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7456,18 +7479,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7482,22 +7505,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7515,22 +7538,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7548,22 +7571,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7581,16 +7604,16 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>26</v>
@@ -7614,22 +7637,22 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7662,7 +7685,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7677,7 +7700,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7695,7 +7718,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7728,7 +7751,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7740,10 +7763,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7761,7 +7784,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7773,7 +7796,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>115</v>
@@ -7794,7 +7817,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7803,13 +7826,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7827,22 +7850,22 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7868,14 +7891,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B209" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7884,16 +7907,16 @@
         <v>25</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>57</v>
       </c>
       <c t="s" r="K209" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
@@ -7912,22 +7935,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7945,7 +7968,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7954,13 +7977,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7978,22 +8001,22 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>291</v>
+        <v>140</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8011,7 +8034,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8026,7 +8049,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8044,7 +8067,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8056,10 +8079,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8077,7 +8100,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8086,13 +8109,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8110,13 +8133,13 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>25</v>
@@ -8125,7 +8148,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8151,14 +8174,14 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>825</v>
+        <v>130</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8167,13 +8190,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>295</v>
+        <v>34</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>67</v>
+        <v>255</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8184,29 +8207,29 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>826</v>
+        <v>133</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>295</v>
+        <v>34</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>296</v>
+        <v>124</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8217,14 +8240,14 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>805</v>
+        <v>140</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8233,13 +8256,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>297</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>186</v>
+        <v>298</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8250,29 +8273,29 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>806</v>
+        <v>151</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8305,7 +8328,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8314,13 +8337,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="K223" s="7">
         <v>32</v>
@@ -8342,29 +8365,29 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="I224" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8379,29 +8402,29 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>84</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8416,25 +8439,25 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>85</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
@@ -8468,7 +8491,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8483,7 +8506,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8501,7 +8524,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8516,7 +8539,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8534,7 +8557,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8546,10 +8569,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8567,7 +8590,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8582,7 +8605,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8600,7 +8623,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8612,7 +8635,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>99</v>
@@ -8633,7 +8656,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8642,7 +8665,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>78</v>
@@ -8666,22 +8689,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8699,7 +8722,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8711,10 +8734,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8747,7 +8770,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8762,7 +8785,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8780,7 +8803,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8795,7 +8818,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8813,7 +8836,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8825,7 +8848,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>39</v>
@@ -8846,7 +8869,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8858,7 +8881,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>118</v>
@@ -8879,7 +8902,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8888,13 +8911,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8912,22 +8935,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8960,7 +8983,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8972,7 +8995,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>215</v>
+        <v>131</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>20</v>
@@ -8980,7 +9003,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -8995,7 +9018,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9004,13 +9027,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>291</v>
+        <v>140</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9028,22 +9051,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9061,19 +9084,19 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>24</v>
@@ -9094,22 +9117,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9127,7 +9150,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9142,7 +9165,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9175,7 +9198,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9190,7 +9213,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9208,7 +9231,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9220,10 +9243,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9241,7 +9264,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9250,13 +9273,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9274,13 +9297,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>25</v>
@@ -9289,7 +9312,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9307,7 +9330,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9316,7 +9339,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>109</v>
@@ -9355,7 +9378,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9364,7 +9387,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>95</v>
@@ -9388,22 +9411,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9421,7 +9444,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9430,13 +9453,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9454,19 +9477,19 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>100</v>
@@ -9487,7 +9510,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9499,7 +9522,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>72</v>
@@ -9520,7 +9543,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9532,10 +9555,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9568,7 +9591,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9577,7 +9600,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>54</v>
@@ -9601,19 +9624,19 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>19</v>
@@ -9634,7 +9657,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9643,10 +9666,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>124</v>
@@ -9667,13 +9690,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>25</v>
@@ -9682,7 +9705,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9700,7 +9723,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9712,7 +9735,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>126</v>
@@ -9748,7 +9771,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9781,7 +9804,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9793,7 +9816,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>96</v>
@@ -9814,7 +9837,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9823,10 +9846,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>85</v>
@@ -9847,13 +9870,13 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>34</v>
@@ -9862,7 +9885,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9880,7 +9903,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9892,10 +9915,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9913,7 +9936,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9928,7 +9951,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9961,7 +9984,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9970,20 +9993,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="K277" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -9998,13 +10021,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>25</v>
@@ -10013,10 +10036,10 @@
         <v>130</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c t="s" r="K278" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
@@ -10035,7 +10058,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10044,20 +10067,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>84</v>
       </c>
       <c t="s" r="K279" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10072,29 +10095,29 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c t="s" r="K280" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10109,7 +10132,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10118,10 +10141,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>41</v>
@@ -10142,22 +10165,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10175,7 +10198,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10187,10 +10210,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10223,7 +10246,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10238,7 +10261,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10256,7 +10279,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10289,7 +10312,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10301,10 +10324,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10322,7 +10345,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10334,7 +10357,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>49</v>
@@ -10355,7 +10378,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10370,7 +10393,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10388,7 +10411,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10436,7 +10459,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10445,13 +10468,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10469,22 +10492,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10502,7 +10525,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10514,7 +10537,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>108</v>
@@ -10535,7 +10558,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10547,7 +10570,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>39</v>
@@ -10583,7 +10606,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10592,13 +10615,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10616,13 +10639,13 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>34</v>
@@ -10631,7 +10654,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10649,7 +10672,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10658,13 +10681,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10682,22 +10705,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10715,7 +10738,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10724,13 +10747,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10748,13 +10771,13 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>34</v>
@@ -10796,7 +10819,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10805,13 +10828,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10829,13 +10852,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>34</v>
@@ -10844,7 +10867,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10862,7 +10885,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10871,13 +10894,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10895,13 +10918,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>34</v>
@@ -10943,7 +10966,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10955,10 +10978,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10976,7 +10999,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -10988,10 +11011,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11009,7 +11032,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11018,13 +11041,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11042,22 +11065,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11075,7 +11098,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11087,7 +11110,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>39</v>
@@ -11108,7 +11131,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11120,7 +11143,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>61</v>
@@ -11156,7 +11179,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11165,13 +11188,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>215</v>
+        <v>131</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11189,13 +11212,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>25</v>
@@ -11204,7 +11227,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11222,7 +11245,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11231,7 +11254,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>122</v>
@@ -11255,22 +11278,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11288,7 +11311,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11297,7 +11320,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>23</v>
@@ -11321,22 +11344,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11354,7 +11377,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11363,10 +11386,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>92</v>
@@ -11387,13 +11410,13 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>25</v>
@@ -11402,7 +11425,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11435,7 +11458,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11447,10 +11470,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11468,7 +11491,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11483,7 +11506,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11501,7 +11524,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11510,7 +11533,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>49</v>
@@ -11534,13 +11557,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>34</v>
@@ -11567,7 +11590,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11576,13 +11599,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11600,22 +11623,22 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11648,7 +11671,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11660,10 +11683,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11681,7 +11704,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11714,7 +11737,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11729,7 +11752,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11762,7 +11785,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11774,17 +11797,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>106</v>
       </c>
       <c t="s" r="K336" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -11799,7 +11822,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11811,10 +11834,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11832,7 +11855,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11844,10 +11867,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11865,7 +11888,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11877,7 +11900,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>42</v>
@@ -11898,7 +11921,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11913,7 +11936,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11946,7 +11969,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11958,10 +11981,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11979,7 +12002,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11991,7 +12014,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>124</v>
@@ -12012,7 +12035,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12021,13 +12044,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12045,19 +12068,19 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>100</v>
@@ -12078,7 +12101,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12087,13 +12110,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12111,13 +12134,13 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>34</v>
@@ -12126,7 +12149,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12159,7 +12182,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12168,13 +12191,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12192,22 +12215,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12225,7 +12248,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12234,13 +12257,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12258,19 +12281,19 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>102</v>
@@ -12291,7 +12314,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12306,7 +12329,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12339,7 +12362,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12348,10 +12371,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>20</v>
@@ -12372,22 +12395,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>364</v>
+        <v>134</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12405,7 +12428,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12414,10 +12437,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>87</v>
@@ -12438,13 +12461,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>25</v>
@@ -12498,7 +12521,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>120</v>
@@ -12536,7 +12559,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12563,13 +12586,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12593,16 +12616,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12632,10 +12655,10 @@
         <v>368</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12710,10 +12733,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>120</v>
@@ -12740,16 +12763,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12776,13 +12799,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12806,7 +12829,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>25</v>
@@ -12815,7 +12838,7 @@
         <v>371</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12845,10 +12868,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12878,10 +12901,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12911,10 +12934,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12944,7 +12967,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>81</v>
@@ -12992,10 +13015,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13025,10 +13048,10 @@
         <v>373</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13061,7 +13084,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13094,7 +13117,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13127,7 +13150,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13169,13 +13192,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13199,10 +13222,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>122</v>
@@ -13232,13 +13255,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>68</v>
@@ -13265,7 +13288,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>34</v>
@@ -13274,7 +13297,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13304,7 +13327,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>117</v>
@@ -13337,10 +13360,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13421,7 +13444,7 @@
         <v>371</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13454,7 +13477,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13481,13 +13504,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13511,7 +13534,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>34</v>
@@ -13520,7 +13543,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13598,10 +13621,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13631,10 +13654,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13664,10 +13687,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13697,7 +13720,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>125</v>
@@ -13727,10 +13750,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>380</v>
@@ -13757,7 +13780,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>25</v>
@@ -13808,17 +13831,19 @@
         <v>25</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>95</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
-      <c r="M403" s="7"/>
+      <c t="s" r="M403" s="7">
+        <v>237</v>
+      </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
       <c t="s" r="A404" s="6">
@@ -13838,16 +13863,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13877,10 +13902,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13910,7 +13935,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>108</v>
@@ -13940,13 +13965,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>26</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13970,7 +13995,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>25</v>
@@ -14009,10 +14034,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14045,7 +14070,7 @@
         <v>369</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14090,17 +14115,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>385</v>
       </c>
       <c t="s" r="K412" s="7">
-        <v>215</v>
+        <v>131</v>
       </c>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14127,17 +14152,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>57</v>
       </c>
       <c t="s" r="K413" s="7">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -14164,10 +14189,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14197,7 +14222,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>70</v>
@@ -14230,10 +14255,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14260,10 +14285,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>386</v>
@@ -14290,13 +14315,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>103</v>
@@ -14329,7 +14354,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>36</v>
@@ -14380,7 +14405,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14410,7 +14435,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>23</v>
@@ -14443,7 +14468,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>100</v>
@@ -14476,7 +14501,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>386</v>
@@ -14506,10 +14531,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>377</v>
@@ -14536,7 +14561,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>16</v>
@@ -14593,7 +14618,7 @@
         <v>391</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14626,7 +14651,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14656,10 +14681,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14692,7 +14717,7 @@
         <v>392</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14719,10 +14744,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>88</v>
@@ -14749,16 +14774,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14785,13 +14810,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>28</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14815,13 +14840,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>393</v>
@@ -14935,10 +14960,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14983,14 +15008,16 @@
         <v>25</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
-      <c r="M441" s="7"/>
+      <c t="s" r="M441" s="7">
+        <v>398</v>
+      </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
       <c t="s" r="A442" s="6">
@@ -15019,7 +15046,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15046,13 +15073,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15076,7 +15103,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>16</v>
@@ -15115,10 +15142,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15151,7 +15178,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15184,19 +15211,19 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>371</v>
@@ -15217,7 +15244,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15265,7 +15292,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15274,13 +15301,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>364</v>
+        <v>134</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15298,19 +15325,19 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>85</v>
@@ -15331,7 +15358,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -15340,7 +15367,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>115</v>
@@ -15364,19 +15391,19 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>24</v>
@@ -15412,7 +15439,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
@@ -15427,7 +15454,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15445,7 +15472,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
@@ -15457,7 +15484,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>38</v>
@@ -15478,7 +15505,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15493,7 +15520,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15526,7 +15553,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15535,7 +15562,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="I460" s="7">
         <v>122</v>
@@ -15559,13 +15586,13 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>16</v>
@@ -15607,27 +15634,27 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="H463" s="8">
         <v>76</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -15642,7 +15669,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
@@ -15654,10 +15681,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15675,7 +15702,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
@@ -15684,10 +15711,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>130</v>
@@ -15723,7 +15750,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
@@ -15735,10 +15762,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -15756,7 +15783,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
@@ -15765,10 +15792,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H468" s="8">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>386</v>
@@ -15789,13 +15816,13 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="H469" s="8">
         <v>16</v>
@@ -15804,7 +15831,7 @@
         <v>396</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15837,7 +15864,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
@@ -15846,13 +15873,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H471" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="I471" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -15870,22 +15897,22 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G472" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="H472" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -15918,7 +15945,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
@@ -15927,13 +15954,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H474" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -15951,22 +15978,22 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G475" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="H475" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -15999,7 +16026,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
@@ -16014,7 +16041,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
@@ -16022,7 +16049,7 @@
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c t="s" r="A478" s="9">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
@@ -16042,7 +16069,7 @@
     <row r="479" ht="65.25" customHeight="1"/>
     <row r="480" ht="17.25" customHeight="1">
       <c t="s" r="A480" s="10">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B480" s="10"/>
       <c r="C480" s="10"/>
@@ -16055,7 +16082,7 @@
       <c r="J480" s="10"/>
       <c r="K480" s="10"/>
       <c t="s" r="L480" s="11">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M480" s="11"/>
       <c r="N480" s="11"/>

--- a/Data/FlightPlan/FPL_12SEP26.xlsx
+++ b/Data/FlightPlan/FPL_12SEP26.xlsx
@@ -188,7 +188,7 @@
     <t>11:05</t>
   </si>
   <si>
-    <t>12:09</t>
+    <t>11:32</t>
   </si>
   <si>
     <t>12:20</t>
@@ -677,6 +677,9 @@
     <t>08:30</t>
   </si>
   <si>
+    <t>08:31</t>
+  </si>
+  <si>
     <t>HGH</t>
   </si>
   <si>
@@ -782,6 +785,9 @@
     <t>VN-A629</t>
   </si>
   <si>
+    <t>08:38</t>
+  </si>
+  <si>
     <t>KUL</t>
   </si>
   <si>
@@ -842,6 +848,9 @@
     <t>VN-A633</t>
   </si>
   <si>
+    <t>08:28</t>
+  </si>
+  <si>
     <t>11:15</t>
   </si>
   <si>
@@ -947,7 +956,7 @@
     <t>06:50</t>
   </si>
   <si>
-    <t>07:48</t>
+    <t>08:04</t>
   </si>
   <si>
     <t>08:20</t>
@@ -1118,129 +1127,129 @@
     <t>01:55</t>
   </si>
   <si>
-    <t>VN-A669</t>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>06:59</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>628 *</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>627 *</t>
+  </si>
+  <si>
+    <t>244 *</t>
+  </si>
+  <si>
+    <t>245 *</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
   </si>
   <si>
     <t>03:55</t>
   </si>
   <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>06:59</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>08:18</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>628 *</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>627 *</t>
-  </si>
-  <si>
-    <t>244 *</t>
-  </si>
-  <si>
-    <t>245 *</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1313,7 +1322,7 @@
     <t>Total Record(s): 392</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 12, 2026 06:31</t>
+    <t xml:space="preserve">Generated on  Sep 12, 2026 07:06</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5652,7 +5661,9 @@
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
+      <c t="s" r="M132" s="7">
+        <v>222</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c t="s" r="A133" s="6">
@@ -5675,13 +5686,13 @@
         <v>77</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="I133" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5705,7 +5716,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>77</v>
@@ -5744,10 +5755,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5780,7 +5791,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5795,7 +5806,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5813,7 +5824,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5825,10 +5836,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5846,7 +5857,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5861,7 +5872,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5879,7 +5890,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5912,7 +5923,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5945,7 +5956,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5960,7 +5971,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5993,7 +6004,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6002,7 +6013,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="I144" s="7">
         <v>132</v>
@@ -6026,13 +6037,13 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>34</v>
@@ -6041,7 +6052,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6059,7 +6070,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6071,7 +6082,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>136</v>
@@ -6092,7 +6103,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6107,7 +6118,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6125,7 +6136,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6137,7 +6148,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>129</v>
@@ -6158,7 +6169,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6191,7 +6202,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6200,10 +6211,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>190</v>
@@ -6239,7 +6250,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6251,15 +6262,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6274,7 +6285,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6286,10 +6297,10 @@
         <v>70</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6307,7 +6318,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6322,7 +6333,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6340,7 +6351,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6388,7 +6399,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6408,7 +6419,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6423,7 +6434,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6432,13 +6443,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6456,13 +6467,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>16</v>
@@ -6471,7 +6482,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6489,7 +6500,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6501,7 +6512,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>146</v>
@@ -6522,7 +6533,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6570,19 +6581,19 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>101</v>
@@ -6603,7 +6614,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6615,7 +6626,7 @@
         <v>67</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>36</v>
@@ -6651,7 +6662,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6673,7 +6684,7 @@
       </c>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>57</v>
+        <v>258</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6688,7 +6699,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6697,13 +6708,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="I167" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6721,13 +6732,13 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>25</v>
@@ -6736,7 +6747,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6754,7 +6765,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6763,10 +6774,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>90</v>
@@ -6787,13 +6798,13 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>25</v>
@@ -6802,7 +6813,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6820,7 +6831,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6853,7 +6864,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6865,10 +6876,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6901,7 +6912,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6913,7 +6924,7 @@
         <v>177</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>87</v>
@@ -6934,7 +6945,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6967,7 +6978,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6979,7 +6990,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>213</v>
@@ -7015,7 +7026,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7024,10 +7035,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>57</v>
@@ -7052,29 +7063,29 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
+        <v>270</v>
+      </c>
+      <c t="s" r="H179" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I179" s="7">
         <v>268</v>
       </c>
-      <c t="s" r="H179" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I179" s="7">
-        <v>266</v>
-      </c>
       <c t="s" r="J179" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="K179" s="7">
         <v>98</v>
       </c>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7089,7 +7100,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7098,10 +7109,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>146</v>
@@ -7122,13 +7133,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>25</v>
@@ -7137,7 +7148,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7155,7 +7166,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7167,7 +7178,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>93</v>
@@ -7203,7 +7214,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7218,11 +7229,13 @@
         <v>54</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
-      <c r="M184" s="7"/>
+      <c t="s" r="M184" s="7">
+        <v>279</v>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c t="s" r="A185" s="6">
@@ -7236,7 +7249,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7251,7 +7264,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7269,7 +7282,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7281,7 +7294,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>100</v>
@@ -7302,7 +7315,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7335,7 +7348,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7368,7 +7381,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7383,7 +7396,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7416,7 +7429,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7425,13 +7438,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7449,13 +7462,13 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>16</v>
@@ -7464,7 +7477,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7482,7 +7495,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7494,7 +7507,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>172</v>
@@ -7515,7 +7528,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7527,7 +7540,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>50</v>
@@ -7563,7 +7576,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7572,18 +7585,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7598,22 +7611,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7631,7 +7644,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7640,13 +7653,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7664,19 +7677,19 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>37</v>
@@ -7697,7 +7710,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7709,7 +7722,7 @@
         <v>179</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>90</v>
@@ -7730,7 +7743,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7778,7 +7791,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7787,18 +7800,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -7813,22 +7826,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7846,22 +7859,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7879,19 +7892,19 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>160</v>
@@ -7912,7 +7925,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7921,7 +7934,7 @@
         <v>155</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>26</v>
@@ -7945,22 +7958,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7993,7 +8006,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8011,11 +8024,11 @@
         <v>190</v>
       </c>
       <c t="s" r="K210" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8030,7 +8043,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8048,7 +8061,7 @@
         <v>85</v>
       </c>
       <c t="s" r="K211" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
@@ -8067,7 +8080,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8076,13 +8089,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>207</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8100,22 +8113,22 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8141,14 +8154,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B215" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8157,7 +8170,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>156</v>
@@ -8185,22 +8198,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8218,7 +8231,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8230,7 +8243,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>117</v>
@@ -8251,7 +8264,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8266,7 +8279,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8284,7 +8297,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8299,7 +8312,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8317,7 +8330,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8350,7 +8363,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8359,13 +8372,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I221" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8383,13 +8396,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>25</v>
@@ -8431,7 +8444,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8443,10 +8456,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8464,7 +8477,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8497,7 +8510,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8509,7 +8522,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>193</v>
@@ -8530,7 +8543,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8578,7 +8591,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8590,17 +8603,17 @@
         <v>173</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="K229" s="7">
         <v>32</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8615,7 +8628,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8624,7 +8637,7 @@
         <v>173</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>142</v>
@@ -8633,7 +8646,7 @@
         <v>183</v>
       </c>
       <c t="s" r="K230" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
@@ -8652,13 +8665,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>173</v>
@@ -8670,7 +8683,7 @@
         <v>85</v>
       </c>
       <c t="s" r="K231" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
@@ -8689,7 +8702,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8701,13 +8714,13 @@
         <v>25</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>87</v>
       </c>
       <c t="s" r="K232" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
@@ -8741,7 +8754,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8774,7 +8787,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8789,14 +8802,14 @@
         <v>19</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="K235" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -8811,7 +8824,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8823,17 +8836,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="K236" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -8848,7 +8861,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8863,7 +8876,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8896,7 +8909,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8929,7 +8942,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8944,7 +8957,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8962,7 +8975,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8974,7 +8987,7 @@
         <v>22</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>39</v>
@@ -8995,7 +9008,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9007,7 +9020,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>123</v>
@@ -9028,7 +9041,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9037,13 +9050,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="I243" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9061,22 +9074,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9109,7 +9122,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9129,7 +9142,7 @@
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9144,7 +9157,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9153,10 +9166,10 @@
         <v>77</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>120</v>
@@ -9177,22 +9190,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9210,19 +9223,19 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>24</v>
@@ -9243,13 +9256,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>77</v>
@@ -9258,7 +9271,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9276,7 +9289,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9291,7 +9304,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9324,7 +9337,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9357,7 +9370,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9390,7 +9403,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9399,13 +9412,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>201</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9423,13 +9436,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>25</v>
@@ -9438,7 +9451,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9456,7 +9469,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9465,7 +9478,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>111</v>
@@ -9504,7 +9517,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9513,7 +9526,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>97</v>
@@ -9537,22 +9550,22 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9570,7 +9583,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9588,11 +9601,11 @@
         <v>171</v>
       </c>
       <c t="s" r="K261" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9607,7 +9620,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9625,7 +9638,7 @@
         <v>137</v>
       </c>
       <c t="s" r="K262" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
@@ -9644,7 +9657,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9666,7 +9679,7 @@
       </c>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9696,7 +9709,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9705,7 +9718,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>54</v>
@@ -9715,7 +9728,9 @@
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
-      <c r="M265" s="7"/>
+      <c t="s" r="M265" s="7">
+        <v>288</v>
+      </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
       <c t="s" r="A266" s="6">
@@ -9729,13 +9744,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>25</v>
@@ -9762,7 +9777,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9771,7 +9786,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>216</v>
@@ -9795,13 +9810,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>25</v>
@@ -9810,7 +9825,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9828,7 +9843,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9837,7 +9852,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>148</v>
@@ -9861,13 +9876,13 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>25</v>
@@ -9876,7 +9891,7 @@
         <v>162</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9894,7 +9909,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9909,7 +9924,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9942,7 +9957,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9962,7 +9977,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -9977,7 +9992,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9989,7 +10004,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>98</v>
@@ -10010,7 +10025,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10022,7 +10037,7 @@
         <v>179</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>87</v>
@@ -10043,7 +10058,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10091,7 +10106,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10100,13 +10115,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>188</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="K278" s="7">
         <v>140</v>
@@ -10128,13 +10143,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>25</v>
@@ -10143,14 +10158,14 @@
         <v>142</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="K279" s="7">
         <v>65</v>
       </c>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10165,7 +10180,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10202,7 +10217,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10214,10 +10229,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="K281" s="7">
         <v>136</v>
@@ -10239,7 +10254,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10251,10 +10266,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10287,7 +10302,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10307,7 +10322,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10322,7 +10337,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10355,7 +10370,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10367,7 +10382,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>170</v>
@@ -10388,7 +10403,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10421,7 +10436,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10454,7 +10469,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10502,7 +10517,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10511,7 +10526,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>190</v>
@@ -10535,13 +10550,13 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>25</v>
@@ -10550,7 +10565,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10568,7 +10583,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10580,7 +10595,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>110</v>
@@ -10601,7 +10616,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10613,7 +10628,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>39</v>
@@ -10649,7 +10664,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10658,10 +10673,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>210</v>
@@ -10669,7 +10684,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10684,13 +10699,13 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>34</v>
@@ -10699,7 +10714,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10717,7 +10732,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10726,13 +10741,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>216</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10750,22 +10765,22 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10783,7 +10798,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10792,7 +10807,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>89</v>
@@ -10816,13 +10831,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>34</v>
@@ -10864,7 +10879,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10876,7 +10891,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>178</v>
@@ -10897,7 +10912,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10912,7 +10927,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10930,7 +10945,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10939,7 +10954,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>89</v>
@@ -10963,13 +10978,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>34</v>
@@ -11011,7 +11026,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11023,15 +11038,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11046,7 +11061,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11079,7 +11094,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11094,7 +11109,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11112,7 +11127,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11124,10 +11139,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11145,7 +11160,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11178,7 +11193,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11190,7 +11205,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>62</v>
@@ -11226,7 +11241,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11235,10 +11250,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>220</v>
@@ -11246,7 +11261,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11261,13 +11276,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>25</v>
@@ -11276,7 +11291,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11294,7 +11309,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11303,7 +11318,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>134</v>
@@ -11327,19 +11342,19 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>178</v>
@@ -11360,7 +11375,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11369,7 +11384,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>23</v>
@@ -11393,19 +11408,19 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>193</v>
@@ -11426,7 +11441,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11435,7 +11450,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>161</v>
@@ -11459,13 +11474,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>25</v>
@@ -11474,7 +11489,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11507,7 +11522,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11540,7 +11555,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11555,7 +11570,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11573,7 +11588,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11582,7 +11597,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>49</v>
@@ -11606,13 +11621,13 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>34</v>
@@ -11639,7 +11654,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11654,7 +11669,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11672,7 +11687,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11684,10 +11699,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11720,7 +11735,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11732,7 +11747,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>216</v>
@@ -11753,7 +11768,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11786,7 +11801,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11801,7 +11816,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11834,7 +11849,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11846,7 +11861,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>108</v>
@@ -11856,7 +11871,7 @@
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -11871,7 +11886,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11886,7 +11901,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11904,7 +11919,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11916,7 +11931,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>149</v>
@@ -11937,7 +11952,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11970,7 +11985,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11985,7 +12000,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12018,7 +12033,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12033,7 +12048,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12051,7 +12066,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12084,7 +12099,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12093,7 +12108,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>49</v>
@@ -12117,13 +12132,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>34</v>
@@ -12139,82 +12154,82 @@
       <c r="M344" s="7"/>
     </row>
     <row r="345" ht="15" customHeight="1">
-      <c t="s" r="A345" s="6">
-        <v>13</v>
-      </c>
-      <c r="B345" s="7">
-        <v>7712</v>
-      </c>
-      <c t="s" r="C345" s="7">
-        <v>14</v>
-      </c>
+      <c r="A345" s="6"/>
+      <c r="B345" s="7"/>
+      <c r="C345" s="7"/>
       <c r="D345" s="7"/>
-      <c t="s" r="E345" s="7">
-        <v>369</v>
-      </c>
-      <c r="F345" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G345" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H345" s="8">
-        <v>356</v>
-      </c>
-      <c t="s" r="I345" s="7">
-        <v>150</v>
-      </c>
-      <c t="s" r="J345" s="7">
-        <v>209</v>
-      </c>
+      <c r="E345" s="7"/>
+      <c r="F345" s="7"/>
+      <c r="G345" s="8"/>
+      <c r="H345" s="8"/>
+      <c r="I345" s="7"/>
+      <c r="J345" s="7"/>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c r="M345" s="7"/>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>7713</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F346" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>34</v>
+        <v>374</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>139</v>
+        <v>292</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>370</v>
+        <v>172</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c r="M346" s="7"/>
     </row>
     <row r="347" ht="14.25" customHeight="1">
-      <c r="A347" s="6"/>
-      <c r="B347" s="7"/>
-      <c r="C347" s="7"/>
+      <c t="s" r="A347" s="6">
+        <v>13</v>
+      </c>
+      <c r="B347" s="7">
+        <v>8891</v>
+      </c>
+      <c t="s" r="C347" s="7">
+        <v>14</v>
+      </c>
       <c r="D347" s="7"/>
-      <c r="E347" s="7"/>
-      <c r="F347" s="7"/>
-      <c r="G347" s="8"/>
-      <c r="H347" s="8"/>
-      <c r="I347" s="7"/>
-      <c r="J347" s="7"/>
+      <c t="s" r="E347" s="7">
+        <v>373</v>
+      </c>
+      <c r="F347" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G347" s="8">
+        <v>374</v>
+      </c>
+      <c t="s" r="H347" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I347" s="7">
+        <v>192</v>
+      </c>
+      <c t="s" r="J347" s="7">
+        <v>263</v>
+      </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
@@ -12224,14 +12239,14 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>8890</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12240,13 +12255,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>289</v>
+        <v>121</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>172</v>
+        <v>375</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12257,29 +12272,29 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>8891</v>
+        <v>8893</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>261</v>
+        <v>104</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12287,17 +12302,17 @@
     </row>
     <row r="350" ht="15" customHeight="1">
       <c t="s" r="A350" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B350" s="7">
-        <v>8892</v>
+        <v>988</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12306,95 +12321,95 @@
         <v>16</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>372</v>
+        <v>56</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c r="M350" s="7"/>
     </row>
     <row r="351" ht="14.25" customHeight="1">
-      <c t="s" r="A351" s="6">
-        <v>13</v>
-      </c>
-      <c r="B351" s="7">
-        <v>8893</v>
-      </c>
-      <c t="s" r="C351" s="7">
-        <v>14</v>
-      </c>
+      <c r="A351" s="6"/>
+      <c r="B351" s="7"/>
+      <c r="C351" s="7"/>
       <c r="D351" s="7"/>
-      <c t="s" r="E351" s="7">
-        <v>371</v>
-      </c>
-      <c r="F351" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G351" s="8">
-        <v>372</v>
-      </c>
-      <c t="s" r="H351" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I351" s="7">
-        <v>263</v>
-      </c>
-      <c t="s" r="J351" s="7">
-        <v>104</v>
-      </c>
+      <c r="E351" s="7"/>
+      <c r="F351" s="7"/>
+      <c r="G351" s="8"/>
+      <c r="H351" s="8"/>
+      <c r="I351" s="7"/>
+      <c r="J351" s="7"/>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c r="M351" s="7"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>988</v>
+        <v>382</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F352" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>56</v>
+        <v>262</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>63</v>
+        <v>378</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c r="A353" s="6"/>
-      <c r="B353" s="7"/>
-      <c r="C353" s="7"/>
+      <c t="s" r="A353" s="6">
+        <v>13</v>
+      </c>
+      <c r="B353" s="7">
+        <v>383</v>
+      </c>
+      <c t="s" r="C353" s="7">
+        <v>14</v>
+      </c>
       <c r="D353" s="7"/>
-      <c r="E353" s="7"/>
-      <c r="F353" s="7"/>
-      <c r="G353" s="8"/>
-      <c r="H353" s="8"/>
-      <c r="I353" s="7"/>
-      <c r="J353" s="7"/>
+      <c t="s" r="E353" s="7">
+        <v>377</v>
+      </c>
+      <c r="F353" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G353" s="8">
+        <v>262</v>
+      </c>
+      <c t="s" r="H353" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I353" s="7">
+        <v>379</v>
+      </c>
+      <c t="s" r="J353" s="7">
+        <v>302</v>
+      </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
@@ -12404,14 +12419,14 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12420,13 +12435,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>260</v>
+        <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>376</v>
+        <v>145</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12437,63 +12452,45 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>260</v>
+        <v>17</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>377</v>
+        <v>283</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>299</v>
+        <v>71</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c r="M355" s="7"/>
     </row>
     <row r="356" ht="14.25" customHeight="1">
-      <c t="s" r="A356" s="6">
-        <v>13</v>
-      </c>
-      <c r="B356" s="7">
-        <v>335</v>
-      </c>
-      <c t="s" r="C356" s="7">
-        <v>14</v>
-      </c>
+      <c r="A356" s="6"/>
+      <c r="B356" s="7"/>
+      <c r="C356" s="7"/>
       <c r="D356" s="7"/>
-      <c t="s" r="E356" s="7">
-        <v>375</v>
-      </c>
-      <c r="F356" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G356" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H356" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I356" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="J356" s="7">
-        <v>119</v>
-      </c>
+      <c r="E356" s="7"/>
+      <c r="F356" s="7"/>
+      <c r="G356" s="8"/>
+      <c r="H356" s="8"/>
+      <c r="I356" s="7"/>
+      <c r="J356" s="7"/>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
@@ -12503,45 +12500,65 @@
         <v>13</v>
       </c>
       <c r="B357" s="7">
-        <v>338</v>
+        <v>120</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
-      <c r="M357" s="7"/>
+      <c t="s" r="M357" s="7">
+        <v>381</v>
+      </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
-      <c r="A358" s="6"/>
-      <c r="B358" s="7"/>
-      <c r="C358" s="7"/>
+      <c t="s" r="A358" s="6">
+        <v>13</v>
+      </c>
+      <c r="B358" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="C358" s="7">
+        <v>14</v>
+      </c>
       <c r="D358" s="7"/>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
-      <c r="G358" s="8"/>
-      <c r="H358" s="8"/>
-      <c r="I358" s="7"/>
-      <c r="J358" s="7"/>
+      <c t="s" r="E358" s="7">
+        <v>380</v>
+      </c>
+      <c r="F358" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G358" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H358" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I358" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J358" s="7">
+        <v>228</v>
+      </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
@@ -12551,14 +12568,14 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>120</v>
+        <v>803</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12567,48 +12584,46 @@
         <v>25</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>34</v>
+        <v>179</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>132</v>
+        <v>293</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
-      <c t="s" r="M359" s="7">
-        <v>379</v>
-      </c>
+      <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c t="s" r="A360" s="6">
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>127</v>
+        <v>804</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>34</v>
+        <v>179</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>57</v>
+        <v>309</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12619,14 +12634,14 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>803</v>
+        <v>1875</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12635,13 +12650,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>179</v>
+        <v>382</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>277</v>
+        <v>121</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12652,63 +12667,45 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>804</v>
+        <v>1876</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>179</v>
+        <v>382</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>281</v>
+        <v>45</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c r="M362" s="7"/>
     </row>
     <row r="363" ht="14.25" customHeight="1">
-      <c t="s" r="A363" s="6">
-        <v>13</v>
-      </c>
-      <c r="B363" s="7">
-        <v>1875</v>
-      </c>
-      <c t="s" r="C363" s="7">
-        <v>14</v>
-      </c>
+      <c r="A363" s="6"/>
+      <c r="B363" s="7"/>
+      <c r="C363" s="7"/>
       <c r="D363" s="7"/>
-      <c t="s" r="E363" s="7">
-        <v>378</v>
-      </c>
-      <c r="F363" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G363" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H363" s="8">
-        <v>380</v>
-      </c>
-      <c t="s" r="I363" s="7">
-        <v>121</v>
-      </c>
-      <c t="s" r="J363" s="7">
-        <v>278</v>
-      </c>
+      <c r="E363" s="7"/>
+      <c r="F363" s="7"/>
+      <c r="G363" s="8"/>
+      <c r="H363" s="8"/>
+      <c r="I363" s="7"/>
+      <c r="J363" s="7"/>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c r="M363" s="7"/>
@@ -12718,45 +12715,65 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>1876</v>
+        <v>1362</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F364" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
-      <c r="M364" s="7"/>
+      <c t="s" r="M364" s="7">
+        <v>156</v>
+      </c>
     </row>
     <row r="365" ht="15" customHeight="1">
-      <c r="A365" s="6"/>
-      <c r="B365" s="7"/>
-      <c r="C365" s="7"/>
+      <c t="s" r="A365" s="6">
+        <v>13</v>
+      </c>
+      <c r="B365" s="7">
+        <v>1363</v>
+      </c>
+      <c t="s" r="C365" s="7">
+        <v>14</v>
+      </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7"/>
-      <c r="F365" s="7"/>
-      <c r="G365" s="8"/>
-      <c r="H365" s="8"/>
-      <c r="I365" s="7"/>
-      <c r="J365" s="7"/>
+      <c t="s" r="E365" s="7">
+        <v>384</v>
+      </c>
+      <c r="F365" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G365" s="8">
+        <v>248</v>
+      </c>
+      <c t="s" r="H365" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I365" s="7">
+        <v>210</v>
+      </c>
+      <c t="s" r="J365" s="7">
+        <v>243</v>
+      </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
@@ -12766,14 +12783,14 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>1362</v>
+        <v>272</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12782,48 +12799,46 @@
         <v>25</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>297</v>
+        <v>144</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>132</v>
+        <v>302</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
-      <c t="s" r="M366" s="7">
-        <v>156</v>
-      </c>
+      <c r="M366" s="7"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
       <c t="s" r="A367" s="6">
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>1363</v>
+        <v>273</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>210</v>
+        <v>273</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>242</v>
+        <v>319</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12834,14 +12849,14 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>272</v>
+        <v>327</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12850,13 +12865,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>299</v>
+        <v>192</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12867,29 +12882,29 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>271</v>
+        <v>201</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>316</v>
+        <v>217</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12900,14 +12915,14 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>327</v>
+        <v>248</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12916,13 +12931,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>192</v>
+        <v>385</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12933,63 +12948,45 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>326</v>
+        <v>249</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c r="M371" s="7"/>
     </row>
     <row r="372" ht="14.25" customHeight="1">
-      <c t="s" r="A372" s="6">
-        <v>13</v>
-      </c>
-      <c r="B372" s="7">
-        <v>248</v>
-      </c>
-      <c t="s" r="C372" s="7">
-        <v>14</v>
-      </c>
+      <c r="A372" s="6"/>
+      <c r="B372" s="7"/>
+      <c r="C372" s="7"/>
       <c r="D372" s="7"/>
-      <c t="s" r="E372" s="7">
-        <v>382</v>
-      </c>
-      <c r="F372" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G372" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H372" s="8">
-        <v>99</v>
-      </c>
-      <c t="s" r="I372" s="7">
-        <v>121</v>
-      </c>
-      <c t="s" r="J372" s="7">
-        <v>383</v>
-      </c>
+      <c r="E372" s="7"/>
+      <c r="F372" s="7"/>
+      <c r="G372" s="8"/>
+      <c r="H372" s="8"/>
+      <c r="I372" s="7"/>
+      <c r="J372" s="7"/>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c r="M372" s="7"/>
@@ -12999,45 +12996,65 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>249</v>
+        <v>969</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
-      <c r="M373" s="7"/>
+      <c t="s" r="M373" s="7">
+        <v>387</v>
+      </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c r="A374" s="6"/>
-      <c r="B374" s="7"/>
-      <c r="C374" s="7"/>
+      <c t="s" r="A374" s="6">
+        <v>13</v>
+      </c>
+      <c r="B374" s="7">
+        <v>986</v>
+      </c>
+      <c t="s" r="C374" s="7">
+        <v>14</v>
+      </c>
       <c r="D374" s="7"/>
-      <c r="E374" s="7"/>
-      <c r="F374" s="7"/>
-      <c r="G374" s="8"/>
-      <c r="H374" s="8"/>
-      <c r="I374" s="7"/>
-      <c r="J374" s="7"/>
+      <c t="s" r="E374" s="7">
+        <v>386</v>
+      </c>
+      <c r="F374" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G374" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H374" s="8">
+        <v>388</v>
+      </c>
+      <c t="s" r="I374" s="7">
+        <v>229</v>
+      </c>
+      <c t="s" r="J374" s="7">
+        <v>146</v>
+      </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
@@ -13047,49 +13064,47 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>969</v>
+        <v>985</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>56</v>
+        <v>388</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>284</v>
+        <v>24</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>299</v>
+        <v>174</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
-      <c t="s" r="M375" s="7">
-        <v>385</v>
-      </c>
+      <c r="M375" s="7"/>
     </row>
     <row r="376" ht="14.25" customHeight="1">
       <c t="s" r="A376" s="6">
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>986</v>
+        <v>322</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13098,13 +13113,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>386</v>
+        <v>25</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13112,114 +13127,114 @@
     </row>
     <row r="377" ht="14.25" customHeight="1">
       <c t="s" r="A377" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B377" s="7">
-        <v>985</v>
+        <v>828</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>386</v>
+        <v>25</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c r="M377" s="7"/>
     </row>
     <row r="378" ht="14.25" customHeight="1">
-      <c t="s" r="A378" s="6">
-        <v>13</v>
-      </c>
-      <c r="B378" s="7">
-        <v>322</v>
-      </c>
-      <c t="s" r="C378" s="7">
-        <v>14</v>
-      </c>
+      <c r="A378" s="6"/>
+      <c r="B378" s="7"/>
+      <c r="C378" s="7"/>
       <c r="D378" s="7"/>
-      <c t="s" r="E378" s="7">
-        <v>384</v>
-      </c>
-      <c r="F378" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G378" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H378" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I378" s="7">
-        <v>28</v>
-      </c>
-      <c t="s" r="J378" s="7">
-        <v>175</v>
-      </c>
+      <c r="E378" s="7"/>
+      <c r="F378" s="7"/>
+      <c r="G378" s="8"/>
+      <c r="H378" s="8"/>
+      <c r="I378" s="7"/>
+      <c r="J378" s="7"/>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c r="M378" s="7"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>828</v>
+        <v>401</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F379" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>35</v>
+        <v>248</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c r="M379" s="7"/>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c r="A380" s="6"/>
-      <c r="B380" s="7"/>
-      <c r="C380" s="7"/>
+      <c t="s" r="A380" s="6">
+        <v>13</v>
+      </c>
+      <c r="B380" s="7">
+        <v>798</v>
+      </c>
+      <c t="s" r="C380" s="7">
+        <v>14</v>
+      </c>
       <c r="D380" s="7"/>
-      <c r="E380" s="7"/>
-      <c r="F380" s="7"/>
-      <c r="G380" s="8"/>
-      <c r="H380" s="8"/>
-      <c r="I380" s="7"/>
-      <c r="J380" s="7"/>
+      <c t="s" r="E380" s="7">
+        <v>389</v>
+      </c>
+      <c r="F380" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G380" s="8">
+        <v>248</v>
+      </c>
+      <c t="s" r="H380" s="8">
+        <v>173</v>
+      </c>
+      <c t="s" r="I380" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J380" s="7">
+        <v>342</v>
+      </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c r="M380" s="7"/>
@@ -13229,29 +13244,29 @@
         <v>13</v>
       </c>
       <c r="B381" s="7">
-        <v>401</v>
+        <v>799</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13262,29 +13277,29 @@
         <v>13</v>
       </c>
       <c r="B382" s="7">
-        <v>798</v>
+        <v>402</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13295,29 +13310,29 @@
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>799</v>
+        <v>441</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>169</v>
+        <v>370</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13328,29 +13343,29 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>126</v>
+        <v>264</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13358,17 +13373,17 @@
     </row>
     <row r="385" ht="15" customHeight="1">
       <c t="s" r="A385" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B385" s="7">
-        <v>441</v>
+        <v>1980</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13377,64 +13392,46 @@
         <v>34</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>17</v>
+        <v>390</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c r="M385" s="7"/>
     </row>
     <row r="386" ht="14.25" customHeight="1">
-      <c t="s" r="A386" s="6">
-        <v>13</v>
-      </c>
-      <c r="B386" s="7">
-        <v>442</v>
-      </c>
-      <c t="s" r="C386" s="7">
-        <v>14</v>
-      </c>
+      <c r="A386" s="6"/>
+      <c r="B386" s="7"/>
+      <c r="C386" s="7"/>
       <c r="D386" s="7"/>
-      <c t="s" r="E386" s="7">
-        <v>387</v>
-      </c>
-      <c r="F386" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G386" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H386" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="I386" s="7">
-        <v>262</v>
-      </c>
-      <c t="s" r="J386" s="7">
-        <v>164</v>
-      </c>
+      <c r="E386" s="7"/>
+      <c r="F386" s="7"/>
+      <c r="G386" s="8"/>
+      <c r="H386" s="8"/>
+      <c r="I386" s="7"/>
+      <c r="J386" s="7"/>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c r="M386" s="7"/>
     </row>
     <row r="387" ht="14.25" customHeight="1">
       <c t="s" r="A387" s="6">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>1980</v>
+        <v>451</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13443,29 +13440,47 @@
         <v>34</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>389</v>
+        <v>273</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c r="M387" s="7"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c r="A388" s="6"/>
-      <c r="B388" s="7"/>
-      <c r="C388" s="7"/>
+      <c t="s" r="A388" s="6">
+        <v>13</v>
+      </c>
+      <c r="B388" s="7">
+        <v>454</v>
+      </c>
+      <c t="s" r="C388" s="7">
+        <v>14</v>
+      </c>
       <c r="D388" s="7"/>
-      <c r="E388" s="7"/>
-      <c r="F388" s="7"/>
-      <c r="G388" s="8"/>
-      <c r="H388" s="8"/>
-      <c r="I388" s="7"/>
-      <c r="J388" s="7"/>
+      <c t="s" r="E388" s="7">
+        <v>392</v>
+      </c>
+      <c r="F388" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G388" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H388" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I388" s="7">
+        <v>128</v>
+      </c>
+      <c t="s" r="J388" s="7">
+        <v>370</v>
+      </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
@@ -13475,14 +13490,14 @@
         <v>13</v>
       </c>
       <c r="B389" s="7">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c t="s" r="C389" s="7">
         <v>14</v>
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13491,13 +13506,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>17</v>
+        <v>286</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13508,63 +13523,45 @@
         <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>17</v>
+        <v>286</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>367</v>
+        <v>213</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c r="M390" s="7"/>
     </row>
     <row r="391" ht="14.25" customHeight="1">
-      <c t="s" r="A391" s="6">
-        <v>13</v>
-      </c>
-      <c r="B391" s="7">
-        <v>495</v>
-      </c>
-      <c t="s" r="C391" s="7">
-        <v>14</v>
-      </c>
+      <c r="A391" s="6"/>
+      <c r="B391" s="7"/>
+      <c r="C391" s="7"/>
       <c r="D391" s="7"/>
-      <c t="s" r="E391" s="7">
-        <v>390</v>
-      </c>
-      <c r="F391" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G391" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H391" s="8">
-        <v>283</v>
-      </c>
-      <c t="s" r="I391" s="7">
-        <v>217</v>
-      </c>
-      <c t="s" r="J391" s="7">
-        <v>325</v>
-      </c>
+      <c r="E391" s="7"/>
+      <c r="F391" s="7"/>
+      <c r="G391" s="8"/>
+      <c r="H391" s="8"/>
+      <c r="I391" s="7"/>
+      <c r="J391" s="7"/>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c r="M391" s="7"/>
@@ -13574,45 +13571,65 @@
         <v>13</v>
       </c>
       <c r="B392" s="7">
-        <v>496</v>
+        <v>121</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F392" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>283</v>
+        <v>34</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>213</v>
+        <v>57</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
-      <c r="M392" s="7"/>
+      <c t="s" r="M392" s="7">
+        <v>394</v>
+      </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
-      <c r="A393" s="6"/>
-      <c r="B393" s="7"/>
-      <c r="C393" s="7"/>
+      <c t="s" r="A393" s="6">
+        <v>13</v>
+      </c>
+      <c r="B393" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="C393" s="7">
+        <v>14</v>
+      </c>
       <c r="D393" s="7"/>
-      <c r="E393" s="7"/>
-      <c r="F393" s="7"/>
-      <c r="G393" s="8"/>
-      <c r="H393" s="8"/>
-      <c r="I393" s="7"/>
-      <c r="J393" s="7"/>
+      <c t="s" r="E393" s="7">
+        <v>393</v>
+      </c>
+      <c r="F393" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G393" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H393" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I393" s="7">
+        <v>190</v>
+      </c>
+      <c t="s" r="J393" s="7">
+        <v>296</v>
+      </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c r="M393" s="7"/>
@@ -13622,49 +13639,47 @@
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>121</v>
+        <v>330</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>32</v>
+        <v>291</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
-      <c t="s" r="M394" s="7">
-        <v>392</v>
-      </c>
+      <c r="M394" s="7"/>
     </row>
     <row r="395" ht="15" customHeight="1">
       <c t="s" r="A395" s="6">
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>321</v>
+        <v>852</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13673,64 +13688,72 @@
         <v>25</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>293</v>
-      </c>
-      <c r="K395" s="7"/>
+        <v>37</v>
+      </c>
+      <c t="s" r="K395" s="7">
+        <v>178</v>
+      </c>
       <c r="L395" s="7"/>
-      <c r="M395" s="7"/>
+      <c t="s" r="M395" s="7">
+        <v>50</v>
+      </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
       <c t="s" r="A396" s="6">
         <v>13</v>
       </c>
       <c r="B396" s="7">
-        <v>330</v>
+        <v>853</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>288</v>
+        <v>38</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>169</v>
-      </c>
-      <c r="K396" s="7"/>
+        <v>72</v>
+      </c>
+      <c t="s" r="K396" s="7">
+        <v>395</v>
+      </c>
       <c r="L396" s="7"/>
-      <c r="M396" s="7"/>
+      <c t="s" r="M396" s="7">
+        <v>122</v>
+      </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
       <c t="s" r="A397" s="6">
         <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>852</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13739,136 +13762,130 @@
         <v>25</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>37</v>
-      </c>
-      <c t="s" r="K397" s="7">
-        <v>178</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="K397" s="7"/>
       <c r="L397" s="7"/>
-      <c t="s" r="M397" s="7">
-        <v>50</v>
-      </c>
+      <c r="M397" s="7"/>
     </row>
     <row r="398" ht="14.25" customHeight="1">
       <c t="s" r="A398" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B398" s="7">
-        <v>853</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>38</v>
+        <v>397</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>72</v>
-      </c>
-      <c t="s" r="K398" s="7">
-        <v>393</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="K398" s="7"/>
       <c r="L398" s="7"/>
-      <c t="s" r="M398" s="7">
-        <v>122</v>
-      </c>
+      <c r="M398" s="7"/>
     </row>
     <row r="399" ht="14.25" customHeight="1">
-      <c t="s" r="A399" s="6">
-        <v>13</v>
-      </c>
-      <c r="B399" s="7">
-        <v>3908</v>
-      </c>
-      <c t="s" r="C399" s="7">
-        <v>14</v>
-      </c>
+      <c r="A399" s="6"/>
+      <c r="B399" s="7"/>
+      <c r="C399" s="7"/>
       <c r="D399" s="7"/>
-      <c t="s" r="E399" s="7">
-        <v>391</v>
-      </c>
-      <c r="F399" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G399" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H399" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="I399" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="J399" s="7">
-        <v>394</v>
-      </c>
+      <c r="E399" s="7"/>
+      <c r="F399" s="7"/>
+      <c r="G399" s="8"/>
+      <c r="H399" s="8"/>
+      <c r="I399" s="7"/>
+      <c r="J399" s="7"/>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c r="M399" s="7"/>
     </row>
     <row r="400" ht="15" customHeight="1">
       <c t="s" r="A400" s="6">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>3909</v>
+        <v>270</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>25</v>
+        <v>274</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>395</v>
+        <v>188</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>396</v>
+        <v>97</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
-      <c r="M400" s="7"/>
+      <c t="s" r="M400" s="7">
+        <v>142</v>
+      </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c r="A401" s="6"/>
-      <c r="B401" s="7"/>
-      <c r="C401" s="7"/>
+      <c t="s" r="A401" s="6">
+        <v>13</v>
+      </c>
+      <c r="B401" s="7">
+        <v>271</v>
+      </c>
+      <c t="s" r="C401" s="7">
+        <v>14</v>
+      </c>
       <c r="D401" s="7"/>
-      <c r="E401" s="7"/>
-      <c r="F401" s="7"/>
-      <c r="G401" s="8"/>
-      <c r="H401" s="8"/>
-      <c r="I401" s="7"/>
-      <c r="J401" s="7"/>
+      <c t="s" r="E401" s="7">
+        <v>399</v>
+      </c>
+      <c r="F401" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G401" s="8">
+        <v>274</v>
+      </c>
+      <c t="s" r="H401" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I401" s="7">
+        <v>205</v>
+      </c>
+      <c t="s" r="J401" s="7">
+        <v>290</v>
+      </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c r="M401" s="7"/>
@@ -13878,14 +13895,14 @@
         <v>13</v>
       </c>
       <c r="B402" s="7">
-        <v>270</v>
+        <v>887</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13894,48 +13911,46 @@
         <v>25</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>272</v>
+        <v>22</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>188</v>
+        <v>302</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
-      <c t="s" r="M402" s="7">
-        <v>142</v>
-      </c>
+      <c r="M402" s="7"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
       <c t="s" r="A403" s="6">
         <v>13</v>
       </c>
       <c r="B403" s="7">
-        <v>271</v>
+        <v>882</v>
       </c>
       <c t="s" r="C403" s="7">
         <v>14</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>272</v>
+        <v>22</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13946,14 +13961,14 @@
         <v>13</v>
       </c>
       <c r="B404" s="7">
-        <v>887</v>
+        <v>352</v>
       </c>
       <c t="s" r="C404" s="7">
         <v>14</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13962,13 +13977,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>299</v>
+        <v>26</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13979,29 +13994,29 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>882</v>
+        <v>353</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>234</v>
+        <v>61</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14012,14 +14027,14 @@
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>352</v>
+        <v>652</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14028,13 +14043,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14045,63 +14060,45 @@
         <v>13</v>
       </c>
       <c r="B407" s="7">
-        <v>353</v>
+        <v>631</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>61</v>
+        <v>383</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c r="M407" s="7"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
-      <c t="s" r="A408" s="6">
-        <v>13</v>
-      </c>
-      <c r="B408" s="7">
-        <v>652</v>
-      </c>
-      <c t="s" r="C408" s="7">
-        <v>14</v>
-      </c>
+      <c r="A408" s="6"/>
+      <c r="B408" s="7"/>
+      <c r="C408" s="7"/>
       <c r="D408" s="7"/>
-      <c t="s" r="E408" s="7">
-        <v>397</v>
-      </c>
-      <c r="F408" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G408" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H408" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I408" s="7">
-        <v>329</v>
-      </c>
-      <c t="s" r="J408" s="7">
-        <v>207</v>
-      </c>
+      <c r="E408" s="7"/>
+      <c r="F408" s="7"/>
+      <c r="G408" s="8"/>
+      <c r="H408" s="8"/>
+      <c r="I408" s="7"/>
+      <c r="J408" s="7"/>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c r="M408" s="7"/>
@@ -14111,62 +14108,88 @@
         <v>13</v>
       </c>
       <c r="B409" s="7">
-        <v>631</v>
+        <v>1630</v>
       </c>
       <c t="s" r="C409" s="7">
         <v>14</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H409" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H409" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I409" s="7">
-        <v>381</v>
+        <v>313</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>209</v>
-      </c>
-      <c r="K409" s="7"/>
+        <v>401</v>
+      </c>
+      <c t="s" r="K409" s="7">
+        <v>143</v>
+      </c>
       <c r="L409" s="7"/>
-      <c r="M409" s="7"/>
+      <c t="s" r="M409" s="7">
+        <v>58</v>
+      </c>
     </row>
     <row r="410" ht="15" customHeight="1">
-      <c r="A410" s="6"/>
-      <c r="B410" s="7"/>
-      <c r="C410" s="7"/>
+      <c t="s" r="A410" s="6">
+        <v>13</v>
+      </c>
+      <c r="B410" s="7">
+        <v>1643</v>
+      </c>
+      <c t="s" r="C410" s="7">
+        <v>14</v>
+      </c>
       <c r="D410" s="7"/>
-      <c r="E410" s="7"/>
-      <c r="F410" s="7"/>
-      <c r="G410" s="8"/>
-      <c r="H410" s="8"/>
-      <c r="I410" s="7"/>
-      <c r="J410" s="7"/>
-      <c r="K410" s="7"/>
+      <c t="s" r="E410" s="7">
+        <v>400</v>
+      </c>
+      <c r="F410" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G410" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H410" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I410" s="7">
+        <v>314</v>
+      </c>
+      <c t="s" r="J410" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="K410" s="7">
+        <v>145</v>
+      </c>
       <c r="L410" s="7"/>
-      <c r="M410" s="7"/>
+      <c t="s" r="M410" s="7">
+        <v>87</v>
+      </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
       <c t="s" r="A411" s="6">
         <v>13</v>
       </c>
       <c r="B411" s="7">
-        <v>1630</v>
+        <v>144</v>
       </c>
       <c t="s" r="C411" s="7">
         <v>14</v>
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14175,87 +14198,79 @@
         <v>25</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>310</v>
+        <v>146</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>399</v>
-      </c>
-      <c t="s" r="K411" s="7">
-        <v>143</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="K411" s="7"/>
       <c r="L411" s="7"/>
-      <c t="s" r="M411" s="7">
-        <v>58</v>
-      </c>
+      <c r="M411" s="7"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
       <c t="s" r="A412" s="6">
         <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>1643</v>
+        <v>409</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>57</v>
-      </c>
-      <c t="s" r="K412" s="7">
-        <v>145</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="K412" s="7"/>
       <c r="L412" s="7"/>
-      <c t="s" r="M412" s="7">
-        <v>87</v>
-      </c>
+      <c r="M412" s="7"/>
     </row>
     <row r="413" ht="14.25" customHeight="1">
       <c t="s" r="A413" s="6">
         <v>13</v>
       </c>
       <c r="B413" s="7">
-        <v>144</v>
+        <v>410</v>
       </c>
       <c t="s" r="C413" s="7">
         <v>14</v>
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>146</v>
+        <v>218</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14263,17 +14278,17 @@
     </row>
     <row r="414" ht="14.25" customHeight="1">
       <c t="s" r="A414" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B414" s="7">
-        <v>409</v>
+        <v>960</v>
       </c>
       <c t="s" r="C414" s="7">
         <v>14</v>
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14282,95 +14297,95 @@
         <v>34</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>247</v>
+        <v>30</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>325</v>
+        <v>204</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>400</v>
+        <v>36</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c r="M414" s="7"/>
     </row>
     <row r="415" ht="15" customHeight="1">
-      <c t="s" r="A415" s="6">
-        <v>13</v>
-      </c>
-      <c r="B415" s="7">
-        <v>410</v>
-      </c>
-      <c t="s" r="C415" s="7">
-        <v>14</v>
-      </c>
+      <c r="A415" s="6"/>
+      <c r="B415" s="7"/>
+      <c r="C415" s="7"/>
       <c r="D415" s="7"/>
-      <c t="s" r="E415" s="7">
-        <v>398</v>
-      </c>
-      <c r="F415" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G415" s="8">
-        <v>247</v>
-      </c>
-      <c t="s" r="H415" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="I415" s="7">
-        <v>218</v>
-      </c>
-      <c t="s" r="J415" s="7">
-        <v>105</v>
-      </c>
+      <c r="E415" s="7"/>
+      <c r="F415" s="7"/>
+      <c r="G415" s="8"/>
+      <c r="H415" s="8"/>
+      <c r="I415" s="7"/>
+      <c r="J415" s="7"/>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c r="M415" s="7"/>
     </row>
     <row r="416" ht="14.25" customHeight="1">
       <c t="s" r="A416" s="6">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B416" s="7">
-        <v>960</v>
+        <v>813</v>
       </c>
       <c t="s" r="C416" s="7">
         <v>14</v>
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>36</v>
+        <v>272</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c r="M416" s="7"/>
     </row>
     <row r="417" ht="14.25" customHeight="1">
-      <c r="A417" s="6"/>
-      <c r="B417" s="7"/>
-      <c r="C417" s="7"/>
+      <c t="s" r="A417" s="6">
+        <v>13</v>
+      </c>
+      <c r="B417" s="7">
+        <v>970</v>
+      </c>
+      <c t="s" r="C417" s="7">
+        <v>14</v>
+      </c>
       <c r="D417" s="7"/>
-      <c r="E417" s="7"/>
-      <c r="F417" s="7"/>
-      <c r="G417" s="8"/>
-      <c r="H417" s="8"/>
-      <c r="I417" s="7"/>
-      <c r="J417" s="7"/>
+      <c t="s" r="E417" s="7">
+        <v>403</v>
+      </c>
+      <c r="F417" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G417" s="8">
+        <v>22</v>
+      </c>
+      <c t="s" r="H417" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I417" s="7">
+        <v>280</v>
+      </c>
+      <c t="s" r="J417" s="7">
+        <v>23</v>
+      </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c r="M417" s="7"/>
@@ -14380,29 +14395,29 @@
         <v>13</v>
       </c>
       <c r="B418" s="7">
-        <v>813</v>
+        <v>889</v>
       </c>
       <c t="s" r="C418" s="7">
         <v>14</v>
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>22</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14413,14 +14428,14 @@
         <v>13</v>
       </c>
       <c r="B419" s="7">
-        <v>970</v>
+        <v>890</v>
       </c>
       <c t="s" r="C419" s="7">
         <v>14</v>
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14432,10 +14447,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>23</v>
+        <v>402</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14446,14 +14461,14 @@
         <v>13</v>
       </c>
       <c r="B420" s="7">
-        <v>889</v>
+        <v>8020</v>
       </c>
       <c t="s" r="C420" s="7">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14462,13 +14477,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>102</v>
+        <v>391</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14476,131 +14491,139 @@
     </row>
     <row r="421" ht="14.25" customHeight="1">
       <c t="s" r="A421" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B421" s="7">
-        <v>890</v>
+        <v>8021</v>
       </c>
       <c t="s" r="C421" s="7">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>325</v>
+        <v>404</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c r="M421" s="7"/>
     </row>
     <row r="422" ht="14.25" customHeight="1">
-      <c t="s" r="A422" s="6">
-        <v>13</v>
-      </c>
-      <c r="B422" s="7">
-        <v>8020</v>
-      </c>
-      <c t="s" r="C422" s="7">
-        <v>74</v>
-      </c>
+      <c r="A422" s="6"/>
+      <c r="B422" s="7"/>
+      <c r="C422" s="7"/>
       <c r="D422" s="7"/>
-      <c t="s" r="E422" s="7">
-        <v>401</v>
-      </c>
-      <c r="F422" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G422" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H422" s="8">
-        <v>318</v>
-      </c>
-      <c t="s" r="I422" s="7">
-        <v>152</v>
-      </c>
-      <c t="s" r="J422" s="7">
-        <v>389</v>
-      </c>
+      <c r="E422" s="7"/>
+      <c r="F422" s="7"/>
+      <c r="G422" s="8"/>
+      <c r="H422" s="8"/>
+      <c r="I422" s="7"/>
+      <c r="J422" s="7"/>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c r="M422" s="7"/>
     </row>
     <row r="423" ht="14.25" customHeight="1">
       <c t="s" r="A423" s="6">
-        <v>43</v>
-      </c>
-      <c r="B423" s="7">
-        <v>8021</v>
+        <v>13</v>
+      </c>
+      <c t="s" r="B423" s="7">
+        <v>406</v>
       </c>
       <c t="s" r="C423" s="7">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>318</v>
+        <v>25</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>402</v>
+        <v>226</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>403</v>
-      </c>
-      <c r="K423" s="7"/>
+        <v>342</v>
+      </c>
+      <c t="s" r="K423" s="7">
+        <v>226</v>
+      </c>
       <c r="L423" s="7"/>
-      <c r="M423" s="7"/>
+      <c t="s" r="M423" s="7">
+        <v>342</v>
+      </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
-      <c r="A424" s="6"/>
-      <c r="B424" s="7"/>
-      <c r="C424" s="7"/>
+      <c t="s" r="A424" s="6">
+        <v>13</v>
+      </c>
+      <c t="s" r="B424" s="7">
+        <v>408</v>
+      </c>
+      <c t="s" r="C424" s="7">
+        <v>14</v>
+      </c>
       <c r="D424" s="7"/>
-      <c r="E424" s="7"/>
-      <c r="F424" s="7"/>
-      <c r="G424" s="8"/>
-      <c r="H424" s="8"/>
-      <c r="I424" s="7"/>
-      <c r="J424" s="7"/>
-      <c r="K424" s="7"/>
+      <c t="s" r="E424" s="7">
+        <v>407</v>
+      </c>
+      <c r="F424" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G424" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H424" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I424" s="7">
+        <v>169</v>
+      </c>
+      <c t="s" r="J424" s="7">
+        <v>200</v>
+      </c>
+      <c t="s" r="K424" s="7">
+        <v>169</v>
+      </c>
       <c r="L424" s="7"/>
-      <c r="M424" s="7"/>
+      <c t="s" r="M424" s="7">
+        <v>200</v>
+      </c>
     </row>
     <row r="425" ht="15" customHeight="1">
       <c t="s" r="A425" s="6">
         <v>13</v>
       </c>
       <c t="s" r="B425" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c t="s" r="C425" s="7">
         <v>14</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14609,20 +14632,20 @@
         <v>25</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c t="s" r="K425" s="7">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>339</v>
+        <v>235</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -14630,51 +14653,51 @@
         <v>13</v>
       </c>
       <c t="s" r="B426" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c t="s" r="C426" s="7">
         <v>14</v>
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c t="s" r="K426" s="7">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>200</v>
+        <v>72</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
       <c t="s" r="A427" s="6">
         <v>13</v>
       </c>
-      <c t="s" r="B427" s="7">
-        <v>407</v>
+      <c r="B427" s="7">
+        <v>154</v>
       </c>
       <c t="s" r="C427" s="7">
         <v>14</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14683,88 +14706,62 @@
         <v>25</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>234</v>
-      </c>
-      <c t="s" r="K427" s="7">
-        <v>250</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="K427" s="7"/>
       <c r="L427" s="7"/>
-      <c t="s" r="M427" s="7">
-        <v>234</v>
-      </c>
+      <c r="M427" s="7"/>
     </row>
     <row r="428" ht="14.25" customHeight="1">
       <c t="s" r="A428" s="6">
         <v>13</v>
       </c>
-      <c t="s" r="B428" s="7">
-        <v>408</v>
+      <c r="B428" s="7">
+        <v>163</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>235</v>
+        <v>164</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>72</v>
-      </c>
-      <c t="s" r="K428" s="7">
-        <v>235</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="K428" s="7"/>
       <c r="L428" s="7"/>
-      <c t="s" r="M428" s="7">
-        <v>72</v>
-      </c>
+      <c r="M428" s="7"/>
     </row>
     <row r="429" ht="14.25" customHeight="1">
-      <c t="s" r="A429" s="6">
-        <v>13</v>
-      </c>
-      <c r="B429" s="7">
-        <v>154</v>
-      </c>
-      <c t="s" r="C429" s="7">
-        <v>14</v>
-      </c>
+      <c r="A429" s="6"/>
+      <c r="B429" s="7"/>
+      <c r="C429" s="7"/>
       <c r="D429" s="7"/>
-      <c t="s" r="E429" s="7">
-        <v>405</v>
-      </c>
-      <c r="F429" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G429" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H429" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="I429" s="7">
-        <v>181</v>
-      </c>
-      <c t="s" r="J429" s="7">
-        <v>73</v>
-      </c>
+      <c r="E429" s="7"/>
+      <c r="F429" s="7"/>
+      <c r="G429" s="8"/>
+      <c r="H429" s="8"/>
+      <c r="I429" s="7"/>
+      <c r="J429" s="7"/>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c r="M429" s="7"/>
@@ -14774,45 +14771,63 @@
         <v>13</v>
       </c>
       <c r="B430" s="7">
-        <v>163</v>
+        <v>507</v>
       </c>
       <c t="s" r="C430" s="7">
         <v>14</v>
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F430" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G430" s="8">
         <v>34</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c r="M430" s="7"/>
     </row>
     <row r="431" ht="14.25" customHeight="1">
-      <c r="A431" s="6"/>
-      <c r="B431" s="7"/>
-      <c r="C431" s="7"/>
+      <c t="s" r="A431" s="6">
+        <v>13</v>
+      </c>
+      <c r="B431" s="7">
+        <v>510</v>
+      </c>
+      <c t="s" r="C431" s="7">
+        <v>14</v>
+      </c>
       <c r="D431" s="7"/>
-      <c r="E431" s="7"/>
-      <c r="F431" s="7"/>
-      <c r="G431" s="8"/>
-      <c r="H431" s="8"/>
-      <c r="I431" s="7"/>
-      <c r="J431" s="7"/>
+      <c t="s" r="E431" s="7">
+        <v>411</v>
+      </c>
+      <c r="F431" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G431" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H431" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I431" s="7">
+        <v>244</v>
+      </c>
+      <c t="s" r="J431" s="7">
+        <v>128</v>
+      </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c r="M431" s="7"/>
@@ -14822,14 +14837,14 @@
         <v>13</v>
       </c>
       <c r="B432" s="7">
-        <v>507</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C432" s="7">
         <v>14</v>
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -14838,13 +14853,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>16</v>
+        <v>359</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>299</v>
+        <v>150</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14852,32 +14867,32 @@
     </row>
     <row r="433" ht="14.25" customHeight="1">
       <c t="s" r="A433" s="6">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B433" s="7">
-        <v>510</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C433" s="7">
         <v>14</v>
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>16</v>
+        <v>359</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>128</v>
+        <v>412</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14910,7 +14925,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -14943,7 +14958,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -14952,7 +14967,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I436" s="7">
         <v>128</v>
@@ -14976,19 +14991,19 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>24</v>
@@ -15009,7 +15024,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -15018,13 +15033,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="I438" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15042,22 +15057,22 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -15090,7 +15105,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15102,7 +15117,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>156</v>
@@ -15110,7 +15125,7 @@
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15125,7 +15140,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15143,11 +15158,11 @@
         <v>190</v>
       </c>
       <c t="s" r="K442" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -15162,7 +15177,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15195,7 +15210,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15204,7 +15219,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="I444" s="7">
         <v>79</v>
@@ -15228,22 +15243,22 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15261,7 +15276,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -15273,10 +15288,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15309,13 +15324,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>34</v>
@@ -15324,7 +15339,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15342,7 +15357,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15390,7 +15405,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15402,10 +15417,10 @@
         <v>179</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15423,7 +15438,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -15456,7 +15471,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -15489,7 +15504,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -15504,7 +15519,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15522,7 +15537,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -15531,10 +15546,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>41</v>
@@ -15555,19 +15570,19 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c t="s" r="J456" s="7">
         <v>218</v>
@@ -15603,7 +15618,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15636,7 +15651,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -15648,7 +15663,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>38</v>
@@ -15669,7 +15684,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15717,7 +15732,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
@@ -15726,7 +15741,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H462" s="8">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c t="s" r="I462" s="7">
         <v>134</v>
@@ -15750,13 +15765,13 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c t="s" r="H463" s="8">
         <v>16</v>
@@ -15798,19 +15813,19 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>191</v>
@@ -15818,7 +15833,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -15833,7 +15848,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -15845,7 +15860,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>171</v>
@@ -15866,7 +15881,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
@@ -15875,7 +15890,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c t="s" r="I467" s="7">
         <v>150</v>
@@ -15914,7 +15929,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -15926,10 +15941,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15947,7 +15962,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -15956,13 +15971,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15980,19 +15995,19 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>205</v>
@@ -16028,7 +16043,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
@@ -16037,13 +16052,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c t="s" r="I473" s="7">
         <v>132</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16061,19 +16076,19 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G474" s="8">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c t="s" r="H474" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J474" s="7">
         <v>188</v>
@@ -16109,7 +16124,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
@@ -16118,10 +16133,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J476" s="7">
         <v>213</v>
@@ -16142,22 +16157,22 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G477" s="8">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c t="s" r="H477" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
@@ -16190,7 +16205,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -16205,7 +16220,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -16213,7 +16228,7 @@
     </row>
     <row r="480" ht="16.5" customHeight="1">
       <c t="s" r="A480" s="9">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B480" s="9"/>
       <c r="C480" s="9"/>
@@ -16233,7 +16248,7 @@
     <row r="481" ht="65.25" customHeight="1"/>
     <row r="482" ht="16.5" customHeight="1">
       <c t="s" r="A482" s="10">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B482" s="10"/>
       <c r="C482" s="10"/>
@@ -16246,7 +16261,7 @@
       <c r="J482" s="10"/>
       <c r="K482" s="10"/>
       <c t="s" r="L482" s="11">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M482" s="11"/>
       <c r="N482" s="11"/>
